--- a/docs/CTDT_K50.xlsx
+++ b/docs/CTDT_K50.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECT\CT553_LVTN\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9EA4B3-7DC7-4D25-BA7E-7B4D5C47D931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58C4EE9E-EF6D-4670-8A91-1FC54D338D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="836" activeTab="1" xr2:uid="{1B4EAF80-CAF0-4237-A3A7-A876EA838391}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="836" xr2:uid="{1B4EAF80-CAF0-4237-A3A7-A876EA838391}"/>
   </bookViews>
   <sheets>
     <sheet name="Danh sách HP" sheetId="4" r:id="rId1"/>
@@ -2263,8 +2263,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2272,11 +2276,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2287,16 +2288,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2693,19 +2693,19 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="9" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
@@ -2811,7 +2811,7 @@
       <c r="A7" s="5">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="29" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="11" t="s">
@@ -2836,7 +2836,7 @@
       <c r="A8" s="5">
         <v>6</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="29" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="11" t="s">
@@ -2845,10 +2845,10 @@
       <c r="D8" s="5">
         <v>4</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="34" t="s">
         <v>196</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="34" t="s">
         <v>399</v>
       </c>
       <c r="G8" s="4"/>
@@ -2863,7 +2863,7 @@
       <c r="A9" s="5">
         <v>7</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="29" t="s">
         <v>33</v>
       </c>
       <c r="C9" s="11" t="s">
@@ -2872,8 +2872,8 @@
       <c r="D9" s="5">
         <v>3</v>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
       <c r="G9" s="19" t="s">
         <v>31</v>
       </c>
@@ -2888,7 +2888,7 @@
       <c r="A10" s="5">
         <v>8</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="29" t="s">
         <v>35</v>
       </c>
       <c r="C10" s="11" t="s">
@@ -2897,8 +2897,8 @@
       <c r="D10" s="5">
         <v>3</v>
       </c>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
       <c r="G10" s="19" t="s">
         <v>33</v>
       </c>
@@ -2913,7 +2913,7 @@
       <c r="A11" s="5">
         <v>9</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="29" t="s">
         <v>37</v>
       </c>
       <c r="C11" s="11" t="s">
@@ -2922,8 +2922,8 @@
       <c r="D11" s="5">
         <v>4</v>
       </c>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
       <c r="G11" s="19" t="s">
         <v>35</v>
       </c>
@@ -2938,7 +2938,7 @@
       <c r="A12" s="5">
         <v>10</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="29" t="s">
         <v>40</v>
       </c>
       <c r="C12" s="11" t="s">
@@ -2947,8 +2947,8 @@
       <c r="D12" s="5">
         <v>3</v>
       </c>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
       <c r="G12" s="19" t="s">
         <v>37</v>
       </c>
@@ -2963,7 +2963,7 @@
       <c r="A13" s="5">
         <v>11</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="29" t="s">
         <v>51</v>
       </c>
       <c r="C13" s="11" t="s">
@@ -2972,8 +2972,8 @@
       <c r="D13" s="5">
         <v>3</v>
       </c>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
       <c r="G13" s="19" t="s">
         <v>40</v>
       </c>
@@ -2988,7 +2988,7 @@
       <c r="A14" s="5">
         <v>12</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="29" t="s">
         <v>61</v>
       </c>
       <c r="C14" s="11" t="s">
@@ -2997,10 +2997,10 @@
       <c r="D14" s="5">
         <v>4</v>
       </c>
-      <c r="E14" s="29" t="s">
+      <c r="E14" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="F14" s="29"/>
+      <c r="F14" s="34"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
       <c r="I14" t="s">
@@ -3013,7 +3013,7 @@
       <c r="A15" s="5">
         <v>13</v>
       </c>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="29" t="s">
         <v>62</v>
       </c>
       <c r="C15" s="11" t="s">
@@ -3022,8 +3022,8 @@
       <c r="D15" s="5">
         <v>3</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
       <c r="G15" s="19" t="s">
         <v>61</v>
       </c>
@@ -3038,7 +3038,7 @@
       <c r="A16" s="5">
         <v>14</v>
       </c>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="29" t="s">
         <v>63</v>
       </c>
       <c r="C16" s="11" t="s">
@@ -3047,8 +3047,8 @@
       <c r="D16" s="5">
         <v>3</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
       <c r="G16" s="19" t="s">
         <v>62</v>
       </c>
@@ -3063,7 +3063,7 @@
       <c r="A17" s="5">
         <v>15</v>
       </c>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="29" t="s">
         <v>64</v>
       </c>
       <c r="C17" s="11" t="s">
@@ -3072,8 +3072,8 @@
       <c r="D17" s="5">
         <v>4</v>
       </c>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
       <c r="G17" s="19" t="s">
         <v>63</v>
       </c>
@@ -3088,7 +3088,7 @@
       <c r="A18" s="5">
         <v>16</v>
       </c>
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="29" t="s">
         <v>65</v>
       </c>
       <c r="C18" s="11" t="s">
@@ -3097,8 +3097,8 @@
       <c r="D18" s="5">
         <v>3</v>
       </c>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
       <c r="G18" s="19" t="s">
         <v>64</v>
       </c>
@@ -3113,7 +3113,7 @@
       <c r="A19" s="5">
         <v>17</v>
       </c>
-      <c r="B19" s="39" t="s">
+      <c r="B19" s="29" t="s">
         <v>66</v>
       </c>
       <c r="C19" s="11" t="s">
@@ -3122,8 +3122,8 @@
       <c r="D19" s="5">
         <v>3</v>
       </c>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
       <c r="G19" s="19" t="s">
         <v>65</v>
       </c>
@@ -3296,7 +3296,7 @@
       <c r="A26" s="5">
         <v>24</v>
       </c>
-      <c r="B26" s="39" t="s">
+      <c r="B26" s="29" t="s">
         <v>73</v>
       </c>
       <c r="C26" s="11" t="s">
@@ -3306,7 +3306,7 @@
         <v>2</v>
       </c>
       <c r="E26" s="5"/>
-      <c r="F26" s="29">
+      <c r="F26" s="34">
         <v>2</v>
       </c>
       <c r="G26" s="4"/>
@@ -3321,7 +3321,7 @@
       <c r="A27" s="5">
         <v>25</v>
       </c>
-      <c r="B27" s="39" t="s">
+      <c r="B27" s="29" t="s">
         <v>74</v>
       </c>
       <c r="C27" s="11" t="s">
@@ -3331,7 +3331,7 @@
         <v>2</v>
       </c>
       <c r="E27" s="5"/>
-      <c r="F27" s="29"/>
+      <c r="F27" s="34"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" t="s">
@@ -3344,7 +3344,7 @@
       <c r="A28" s="5">
         <v>26</v>
       </c>
-      <c r="B28" s="39" t="s">
+      <c r="B28" s="29" t="s">
         <v>75</v>
       </c>
       <c r="C28" s="11" t="s">
@@ -3354,7 +3354,7 @@
         <v>2</v>
       </c>
       <c r="E28" s="5"/>
-      <c r="F28" s="29"/>
+      <c r="F28" s="34"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" t="s">
@@ -3367,7 +3367,7 @@
       <c r="A29" s="5">
         <v>27</v>
       </c>
-      <c r="B29" s="39" t="s">
+      <c r="B29" s="29" t="s">
         <v>76</v>
       </c>
       <c r="C29" s="11" t="s">
@@ -3377,7 +3377,7 @@
         <v>2</v>
       </c>
       <c r="E29" s="5"/>
-      <c r="F29" s="29"/>
+      <c r="F29" s="34"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" t="s">
@@ -3390,7 +3390,7 @@
       <c r="A30" s="5">
         <v>28</v>
       </c>
-      <c r="B30" s="39" t="s">
+      <c r="B30" s="29" t="s">
         <v>77</v>
       </c>
       <c r="C30" s="11" t="s">
@@ -3400,7 +3400,7 @@
         <v>2</v>
       </c>
       <c r="E30" s="5"/>
-      <c r="F30" s="29"/>
+      <c r="F30" s="34"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" t="s">
@@ -3413,7 +3413,7 @@
       <c r="A31" s="5">
         <v>29</v>
       </c>
-      <c r="B31" s="39" t="s">
+      <c r="B31" s="29" t="s">
         <v>78</v>
       </c>
       <c r="C31" s="11" t="s">
@@ -3423,7 +3423,7 @@
         <v>2</v>
       </c>
       <c r="E31" s="5"/>
-      <c r="F31" s="29"/>
+      <c r="F31" s="34"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" t="s">
@@ -3436,7 +3436,7 @@
       <c r="A32" s="5">
         <v>30</v>
       </c>
-      <c r="B32" s="39" t="s">
+      <c r="B32" s="29" t="s">
         <v>79</v>
       </c>
       <c r="C32" s="11" t="s">
@@ -3446,7 +3446,7 @@
         <v>2</v>
       </c>
       <c r="E32" s="5"/>
-      <c r="F32" s="29"/>
+      <c r="F32" s="34"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" t="s">
@@ -3608,19 +3608,19 @@
       <c r="K38" s="4"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A39" s="30" t="s">
+      <c r="A39" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="B39" s="30"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="30"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="30"/>
-      <c r="J39" s="30"/>
-      <c r="K39" s="30"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="32"/>
+      <c r="J39" s="32"/>
+      <c r="K39" s="32"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="5"/>
@@ -3636,19 +3636,19 @@
       <c r="K40" s="7"/>
     </row>
     <row r="41" spans="1:11" s="10" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="31" t="s">
+      <c r="A41" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="B41" s="31"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="31"/>
-      <c r="H41" s="31"/>
-      <c r="I41" s="31"/>
-      <c r="J41" s="31"/>
-      <c r="K41" s="31"/>
+      <c r="B41" s="33"/>
+      <c r="C41" s="33"/>
+      <c r="D41" s="33"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="33"/>
+      <c r="G41" s="33"/>
+      <c r="H41" s="33"/>
+      <c r="I41" s="33"/>
+      <c r="J41" s="33"/>
+      <c r="K41" s="33"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
@@ -4044,19 +4044,19 @@
       <c r="K56" s="4"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A57" s="30" t="s">
+      <c r="A57" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="B57" s="30"/>
-      <c r="C57" s="30"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="30"/>
-      <c r="F57" s="30"/>
-      <c r="G57" s="30"/>
-      <c r="H57" s="30"/>
-      <c r="I57" s="30"/>
-      <c r="J57" s="30"/>
-      <c r="K57" s="30"/>
+      <c r="B57" s="32"/>
+      <c r="C57" s="32"/>
+      <c r="D57" s="32"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="32"/>
+      <c r="I57" s="32"/>
+      <c r="J57" s="32"/>
+      <c r="K57" s="32"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="5"/>
@@ -4072,25 +4072,25 @@
       <c r="K58" s="7"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A59" s="31" t="s">
+      <c r="A59" s="33" t="s">
         <v>275</v>
       </c>
-      <c r="B59" s="31"/>
-      <c r="C59" s="31"/>
-      <c r="D59" s="31"/>
-      <c r="E59" s="31"/>
-      <c r="F59" s="31"/>
-      <c r="G59" s="31"/>
-      <c r="H59" s="31"/>
-      <c r="I59" s="31"/>
-      <c r="J59" s="31"/>
-      <c r="K59" s="31"/>
+      <c r="B59" s="33"/>
+      <c r="C59" s="33"/>
+      <c r="D59" s="33"/>
+      <c r="E59" s="33"/>
+      <c r="F59" s="33"/>
+      <c r="G59" s="33"/>
+      <c r="H59" s="33"/>
+      <c r="I59" s="33"/>
+      <c r="J59" s="33"/>
+      <c r="K59" s="33"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="5">
         <v>52</v>
       </c>
-      <c r="B60" s="39" t="s">
+      <c r="B60" s="29" t="s">
         <v>98</v>
       </c>
       <c r="C60" s="11" t="s">
@@ -4102,7 +4102,7 @@
       <c r="E60" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="F60" s="29">
+      <c r="F60" s="34">
         <v>3</v>
       </c>
       <c r="G60" s="19" t="s">
@@ -4119,7 +4119,7 @@
       <c r="A61" s="5">
         <v>53</v>
       </c>
-      <c r="B61" s="39" t="s">
+      <c r="B61" s="29" t="s">
         <v>101</v>
       </c>
       <c r="C61" s="11" t="s">
@@ -4131,7 +4131,7 @@
       <c r="E61" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="F61" s="29"/>
+      <c r="F61" s="34"/>
       <c r="G61" s="19" t="s">
         <v>92</v>
       </c>
@@ -4146,7 +4146,7 @@
       <c r="A62" s="5">
         <v>54</v>
       </c>
-      <c r="B62" s="39" t="s">
+      <c r="B62" s="29" t="s">
         <v>102</v>
       </c>
       <c r="C62" s="11" t="s">
@@ -4158,7 +4158,7 @@
       <c r="E62" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="F62" s="29"/>
+      <c r="F62" s="34"/>
       <c r="G62" s="19" t="s">
         <v>92</v>
       </c>
@@ -4466,7 +4466,7 @@
       <c r="A74" s="5">
         <v>66</v>
       </c>
-      <c r="B74" s="39" t="s">
+      <c r="B74" s="29" t="s">
         <v>114</v>
       </c>
       <c r="C74" s="11" t="s">
@@ -4476,7 +4476,7 @@
         <v>3</v>
       </c>
       <c r="E74" s="5"/>
-      <c r="F74" s="29">
+      <c r="F74" s="34">
         <v>3</v>
       </c>
       <c r="G74" s="4" t="s">
@@ -4493,7 +4493,7 @@
       <c r="A75" s="5">
         <v>67</v>
       </c>
-      <c r="B75" s="39" t="s">
+      <c r="B75" s="29" t="s">
         <v>115</v>
       </c>
       <c r="C75" s="11" t="s">
@@ -4503,7 +4503,7 @@
         <v>3</v>
       </c>
       <c r="E75" s="5"/>
-      <c r="F75" s="29"/>
+      <c r="F75" s="34"/>
       <c r="G75" s="4" t="s">
         <v>92</v>
       </c>
@@ -4518,7 +4518,7 @@
       <c r="A76" s="5">
         <v>68</v>
       </c>
-      <c r="B76" s="39" t="s">
+      <c r="B76" s="29" t="s">
         <v>116</v>
       </c>
       <c r="C76" s="11" t="s">
@@ -4528,7 +4528,7 @@
         <v>3</v>
       </c>
       <c r="E76" s="5"/>
-      <c r="F76" s="29"/>
+      <c r="F76" s="34"/>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
       <c r="I76" t="s">
@@ -4541,7 +4541,7 @@
       <c r="A77" s="5">
         <v>69</v>
       </c>
-      <c r="B77" s="39" t="s">
+      <c r="B77" s="29" t="s">
         <v>117</v>
       </c>
       <c r="C77" s="11" t="s">
@@ -4551,7 +4551,7 @@
         <v>3</v>
       </c>
       <c r="E77" s="5"/>
-      <c r="F77" s="29"/>
+      <c r="F77" s="34"/>
       <c r="G77" s="4" t="s">
         <v>92</v>
       </c>
@@ -4593,7 +4593,7 @@
       <c r="A79" s="5">
         <v>71</v>
       </c>
-      <c r="B79" s="39" t="s">
+      <c r="B79" s="29" t="s">
         <v>119</v>
       </c>
       <c r="C79" s="11" t="s">
@@ -4603,7 +4603,7 @@
         <v>3</v>
       </c>
       <c r="E79" s="5"/>
-      <c r="F79" s="34">
+      <c r="F79" s="35">
         <v>15</v>
       </c>
       <c r="G79" s="4"/>
@@ -4618,7 +4618,7 @@
       <c r="A80" s="5">
         <v>72</v>
       </c>
-      <c r="B80" s="39" t="s">
+      <c r="B80" s="29" t="s">
         <v>120</v>
       </c>
       <c r="C80" s="11" t="s">
@@ -4628,7 +4628,7 @@
         <v>15</v>
       </c>
       <c r="E80" s="5"/>
-      <c r="F80" s="35"/>
+      <c r="F80" s="36"/>
       <c r="G80" s="4" t="s">
         <v>208</v>
       </c>
@@ -4643,7 +4643,7 @@
       <c r="A81" s="5">
         <v>73</v>
       </c>
-      <c r="B81" s="39" t="s">
+      <c r="B81" s="29" t="s">
         <v>121</v>
       </c>
       <c r="C81" s="11" t="s">
@@ -4653,7 +4653,7 @@
         <v>6</v>
       </c>
       <c r="E81" s="5"/>
-      <c r="F81" s="35"/>
+      <c r="F81" s="36"/>
       <c r="G81" s="4" t="s">
         <v>208</v>
       </c>
@@ -4668,7 +4668,7 @@
       <c r="A82" s="5">
         <v>74</v>
       </c>
-      <c r="B82" s="39" t="s">
+      <c r="B82" s="29" t="s">
         <v>122</v>
       </c>
       <c r="C82" s="11" t="s">
@@ -4678,7 +4678,7 @@
         <v>3</v>
       </c>
       <c r="E82" s="5"/>
-      <c r="F82" s="35"/>
+      <c r="F82" s="36"/>
       <c r="G82" s="4"/>
       <c r="H82" s="4"/>
       <c r="I82" t="s">
@@ -4691,7 +4691,7 @@
       <c r="A83" s="5">
         <v>75</v>
       </c>
-      <c r="B83" s="39" t="s">
+      <c r="B83" s="29" t="s">
         <v>123</v>
       </c>
       <c r="C83" s="11" t="s">
@@ -4701,7 +4701,7 @@
         <v>3</v>
       </c>
       <c r="E83" s="5"/>
-      <c r="F83" s="35"/>
+      <c r="F83" s="36"/>
       <c r="G83" s="4"/>
       <c r="H83" s="4"/>
       <c r="I83" t="s">
@@ -4714,7 +4714,7 @@
       <c r="A84" s="5">
         <v>76</v>
       </c>
-      <c r="B84" s="39" t="s">
+      <c r="B84" s="29" t="s">
         <v>124</v>
       </c>
       <c r="C84" s="11" t="s">
@@ -4724,7 +4724,7 @@
         <v>3</v>
       </c>
       <c r="E84" s="5"/>
-      <c r="F84" s="35"/>
+      <c r="F84" s="36"/>
       <c r="G84" s="4"/>
       <c r="H84" s="4"/>
       <c r="I84" t="s">
@@ -4737,7 +4737,7 @@
       <c r="A85" s="5">
         <v>77</v>
       </c>
-      <c r="B85" s="39" t="s">
+      <c r="B85" s="29" t="s">
         <v>125</v>
       </c>
       <c r="C85" s="11" t="s">
@@ -4747,7 +4747,7 @@
         <v>3</v>
       </c>
       <c r="E85" s="5"/>
-      <c r="F85" s="35"/>
+      <c r="F85" s="36"/>
       <c r="G85" s="4" t="s">
         <v>93</v>
       </c>
@@ -4762,7 +4762,7 @@
       <c r="A86" s="5">
         <v>78</v>
       </c>
-      <c r="B86" s="39" t="s">
+      <c r="B86" s="29" t="s">
         <v>126</v>
       </c>
       <c r="C86" s="11" t="s">
@@ -4772,7 +4772,7 @@
         <v>3</v>
       </c>
       <c r="E86" s="5"/>
-      <c r="F86" s="35"/>
+      <c r="F86" s="36"/>
       <c r="G86" s="4" t="s">
         <v>92</v>
       </c>
@@ -4787,7 +4787,7 @@
       <c r="A87" s="5">
         <v>79</v>
       </c>
-      <c r="B87" s="39" t="s">
+      <c r="B87" s="29" t="s">
         <v>127</v>
       </c>
       <c r="C87" s="11" t="s">
@@ -4797,7 +4797,7 @@
         <v>3</v>
       </c>
       <c r="E87" s="5"/>
-      <c r="F87" s="35"/>
+      <c r="F87" s="36"/>
       <c r="G87" s="4"/>
       <c r="H87" s="4"/>
       <c r="I87" t="s">
@@ -4810,7 +4810,7 @@
       <c r="A88" s="5">
         <v>80</v>
       </c>
-      <c r="B88" s="39" t="s">
+      <c r="B88" s="29" t="s">
         <v>128</v>
       </c>
       <c r="C88" s="11" t="s">
@@ -4820,7 +4820,7 @@
         <v>3</v>
       </c>
       <c r="E88" s="5"/>
-      <c r="F88" s="35"/>
+      <c r="F88" s="36"/>
       <c r="G88" s="4" t="s">
         <v>93</v>
       </c>
@@ -4835,7 +4835,7 @@
       <c r="A89" s="5">
         <v>81</v>
       </c>
-      <c r="B89" s="39" t="s">
+      <c r="B89" s="29" t="s">
         <v>129</v>
       </c>
       <c r="C89" s="11" t="s">
@@ -4845,7 +4845,7 @@
         <v>3</v>
       </c>
       <c r="E89" s="5"/>
-      <c r="F89" s="35"/>
+      <c r="F89" s="36"/>
       <c r="G89" s="4" t="s">
         <v>13</v>
       </c>
@@ -4860,7 +4860,7 @@
       <c r="A90" s="5">
         <v>82</v>
       </c>
-      <c r="B90" s="39" t="s">
+      <c r="B90" s="29" t="s">
         <v>130</v>
       </c>
       <c r="C90" s="11" t="s">
@@ -4870,7 +4870,7 @@
         <v>3</v>
       </c>
       <c r="E90" s="5"/>
-      <c r="F90" s="36"/>
+      <c r="F90" s="37"/>
       <c r="G90" s="4" t="s">
         <v>93</v>
       </c>
@@ -4882,34 +4882,34 @@
       <c r="K90" s="4"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A91" s="30" t="s">
+      <c r="A91" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="B91" s="30"/>
-      <c r="C91" s="30"/>
-      <c r="D91" s="30"/>
-      <c r="E91" s="30"/>
-      <c r="F91" s="30"/>
-      <c r="G91" s="30"/>
-      <c r="H91" s="30"/>
-      <c r="I91" s="30"/>
-      <c r="J91" s="30"/>
-      <c r="K91" s="30"/>
+      <c r="B91" s="32"/>
+      <c r="C91" s="32"/>
+      <c r="D91" s="32"/>
+      <c r="E91" s="32"/>
+      <c r="F91" s="32"/>
+      <c r="G91" s="32"/>
+      <c r="H91" s="32"/>
+      <c r="I91" s="32"/>
+      <c r="J91" s="32"/>
+      <c r="K91" s="32"/>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A92" s="30" t="s">
+      <c r="A92" s="32" t="s">
         <v>202</v>
       </c>
-      <c r="B92" s="30"/>
-      <c r="C92" s="30"/>
-      <c r="D92" s="30"/>
-      <c r="E92" s="30"/>
-      <c r="F92" s="30"/>
-      <c r="G92" s="30"/>
-      <c r="H92" s="30"/>
-      <c r="I92" s="30"/>
-      <c r="J92" s="30"/>
-      <c r="K92" s="30"/>
+      <c r="B92" s="32"/>
+      <c r="C92" s="32"/>
+      <c r="D92" s="32"/>
+      <c r="E92" s="32"/>
+      <c r="F92" s="32"/>
+      <c r="G92" s="32"/>
+      <c r="H92" s="32"/>
+      <c r="I92" s="32"/>
+      <c r="J92" s="32"/>
+      <c r="K92" s="32"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="13"/>
@@ -4925,19 +4925,19 @@
       <c r="K93" s="13"/>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A94" s="31" t="s">
+      <c r="A94" s="33" t="s">
         <v>276</v>
       </c>
-      <c r="B94" s="31"/>
-      <c r="C94" s="31"/>
-      <c r="D94" s="31"/>
-      <c r="E94" s="31"/>
-      <c r="F94" s="31"/>
-      <c r="G94" s="31"/>
-      <c r="H94" s="31"/>
-      <c r="I94" s="31"/>
-      <c r="J94" s="31"/>
-      <c r="K94" s="31"/>
+      <c r="B94" s="33"/>
+      <c r="C94" s="33"/>
+      <c r="D94" s="33"/>
+      <c r="E94" s="33"/>
+      <c r="F94" s="33"/>
+      <c r="G94" s="33"/>
+      <c r="H94" s="33"/>
+      <c r="I94" s="33"/>
+      <c r="J94" s="33"/>
+      <c r="K94" s="33"/>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" s="16">
@@ -5103,7 +5103,7 @@
       <c r="A101" s="16">
         <v>89</v>
       </c>
-      <c r="B101" s="40" t="s">
+      <c r="B101" s="30" t="s">
         <v>287</v>
       </c>
       <c r="C101" s="17" t="s">
@@ -5112,10 +5112,10 @@
       <c r="D101" s="16">
         <v>3</v>
       </c>
-      <c r="E101" s="29" t="s">
+      <c r="E101" s="34" t="s">
         <v>356</v>
       </c>
-      <c r="F101" s="29" t="s">
+      <c r="F101" s="34" t="s">
         <v>398</v>
       </c>
       <c r="G101" s="4"/>
@@ -5130,7 +5130,7 @@
       <c r="A102" s="16">
         <v>90</v>
       </c>
-      <c r="B102" s="40" t="s">
+      <c r="B102" s="30" t="s">
         <v>288</v>
       </c>
       <c r="C102" s="17" t="s">
@@ -5139,8 +5139,8 @@
       <c r="D102" s="16">
         <v>3</v>
       </c>
-      <c r="E102" s="29"/>
-      <c r="F102" s="29"/>
+      <c r="E102" s="34"/>
+      <c r="F102" s="34"/>
       <c r="G102" s="23" t="s">
         <v>91</v>
       </c>
@@ -5155,7 +5155,7 @@
       <c r="A103" s="16">
         <v>91</v>
       </c>
-      <c r="B103" s="40" t="s">
+      <c r="B103" s="30" t="s">
         <v>289</v>
       </c>
       <c r="C103" s="17" t="s">
@@ -5164,8 +5164,8 @@
       <c r="D103" s="16">
         <v>3</v>
       </c>
-      <c r="E103" s="29"/>
-      <c r="F103" s="29"/>
+      <c r="E103" s="34"/>
+      <c r="F103" s="34"/>
       <c r="G103" s="23" t="s">
         <v>281</v>
       </c>
@@ -5180,7 +5180,7 @@
       <c r="A104" s="16">
         <v>92</v>
       </c>
-      <c r="B104" s="40" t="s">
+      <c r="B104" s="30" t="s">
         <v>290</v>
       </c>
       <c r="C104" s="17" t="s">
@@ -5189,8 +5189,8 @@
       <c r="D104" s="16">
         <v>3</v>
       </c>
-      <c r="E104" s="29"/>
-      <c r="F104" s="29"/>
+      <c r="E104" s="34"/>
+      <c r="F104" s="34"/>
       <c r="G104" s="23" t="s">
         <v>91</v>
       </c>
@@ -5205,7 +5205,7 @@
       <c r="A105" s="16">
         <v>93</v>
       </c>
-      <c r="B105" s="40" t="s">
+      <c r="B105" s="30" t="s">
         <v>291</v>
       </c>
       <c r="C105" s="17" t="s">
@@ -5214,8 +5214,8 @@
       <c r="D105" s="16">
         <v>2</v>
       </c>
-      <c r="E105" s="29"/>
-      <c r="F105" s="29"/>
+      <c r="E105" s="34"/>
+      <c r="F105" s="34"/>
       <c r="G105" s="4"/>
       <c r="H105" s="23"/>
       <c r="I105" t="s">
@@ -5228,7 +5228,7 @@
       <c r="A106" s="16">
         <v>94</v>
       </c>
-      <c r="B106" s="40" t="s">
+      <c r="B106" s="30" t="s">
         <v>292</v>
       </c>
       <c r="C106" s="17" t="s">
@@ -5237,8 +5237,8 @@
       <c r="D106" s="16">
         <v>2</v>
       </c>
-      <c r="E106" s="29"/>
-      <c r="F106" s="29"/>
+      <c r="E106" s="34"/>
+      <c r="F106" s="34"/>
       <c r="G106" s="23" t="s">
         <v>281</v>
       </c>
@@ -5253,7 +5253,7 @@
       <c r="A107" s="16">
         <v>95</v>
       </c>
-      <c r="B107" s="40" t="s">
+      <c r="B107" s="30" t="s">
         <v>293</v>
       </c>
       <c r="C107" s="17" t="s">
@@ -5262,10 +5262,10 @@
       <c r="D107" s="16">
         <v>2</v>
       </c>
-      <c r="E107" s="29" t="s">
+      <c r="E107" s="34" t="s">
         <v>357</v>
       </c>
-      <c r="F107" s="29"/>
+      <c r="F107" s="34"/>
       <c r="G107" s="4"/>
       <c r="H107" s="23"/>
       <c r="I107" t="s">
@@ -5278,7 +5278,7 @@
       <c r="A108" s="16">
         <v>96</v>
       </c>
-      <c r="B108" s="40" t="s">
+      <c r="B108" s="30" t="s">
         <v>294</v>
       </c>
       <c r="C108" s="17" t="s">
@@ -5287,8 +5287,8 @@
       <c r="D108" s="16">
         <v>3</v>
       </c>
-      <c r="E108" s="29"/>
-      <c r="F108" s="29"/>
+      <c r="E108" s="34"/>
+      <c r="F108" s="34"/>
       <c r="G108" s="23" t="s">
         <v>359</v>
       </c>
@@ -5303,7 +5303,7 @@
       <c r="A109" s="16">
         <v>97</v>
       </c>
-      <c r="B109" s="40" t="s">
+      <c r="B109" s="30" t="s">
         <v>295</v>
       </c>
       <c r="C109" s="17" t="s">
@@ -5312,8 +5312,8 @@
       <c r="D109" s="16">
         <v>3</v>
       </c>
-      <c r="E109" s="29"/>
-      <c r="F109" s="29"/>
+      <c r="E109" s="34"/>
+      <c r="F109" s="34"/>
       <c r="G109" s="23" t="s">
         <v>92</v>
       </c>
@@ -5328,7 +5328,7 @@
       <c r="A110" s="16">
         <v>98</v>
       </c>
-      <c r="B110" s="40" t="s">
+      <c r="B110" s="30" t="s">
         <v>296</v>
       </c>
       <c r="C110" s="17" t="s">
@@ -5337,8 +5337,8 @@
       <c r="D110" s="16">
         <v>3</v>
       </c>
-      <c r="E110" s="29"/>
-      <c r="F110" s="29"/>
+      <c r="E110" s="34"/>
+      <c r="F110" s="34"/>
       <c r="G110" s="4"/>
       <c r="H110" s="23"/>
       <c r="I110" t="s">
@@ -5351,7 +5351,7 @@
       <c r="A111" s="16">
         <v>99</v>
       </c>
-      <c r="B111" s="40" t="s">
+      <c r="B111" s="30" t="s">
         <v>297</v>
       </c>
       <c r="C111" s="17" t="s">
@@ -5360,8 +5360,8 @@
       <c r="D111" s="16">
         <v>3</v>
       </c>
-      <c r="E111" s="29"/>
-      <c r="F111" s="29"/>
+      <c r="E111" s="34"/>
+      <c r="F111" s="34"/>
       <c r="G111" s="4"/>
       <c r="H111" s="23"/>
       <c r="I111" t="s">
@@ -5374,7 +5374,7 @@
       <c r="A112" s="16">
         <v>100</v>
       </c>
-      <c r="B112" s="40" t="s">
+      <c r="B112" s="30" t="s">
         <v>298</v>
       </c>
       <c r="C112" s="17" t="s">
@@ -5383,8 +5383,8 @@
       <c r="D112" s="16">
         <v>2</v>
       </c>
-      <c r="E112" s="29"/>
-      <c r="F112" s="29"/>
+      <c r="E112" s="34"/>
+      <c r="F112" s="34"/>
       <c r="G112" s="23" t="s">
         <v>91</v>
       </c>
@@ -5532,7 +5532,7 @@
       <c r="A118" s="16">
         <v>106</v>
       </c>
-      <c r="B118" s="40" t="s">
+      <c r="B118" s="30" t="s">
         <v>304</v>
       </c>
       <c r="C118" s="17" t="s">
@@ -5542,7 +5542,7 @@
         <v>15</v>
       </c>
       <c r="E118" s="16"/>
-      <c r="F118" s="29">
+      <c r="F118" s="34">
         <v>15</v>
       </c>
       <c r="G118" s="4" t="s">
@@ -5559,7 +5559,7 @@
       <c r="A119" s="16">
         <v>107</v>
       </c>
-      <c r="B119" s="40" t="s">
+      <c r="B119" s="30" t="s">
         <v>305</v>
       </c>
       <c r="C119" s="17" t="s">
@@ -5569,7 +5569,7 @@
         <v>6</v>
       </c>
       <c r="E119" s="16"/>
-      <c r="F119" s="29"/>
+      <c r="F119" s="34"/>
       <c r="G119" s="4" t="s">
         <v>208</v>
       </c>
@@ -5584,7 +5584,7 @@
       <c r="A120" s="16">
         <v>108</v>
       </c>
-      <c r="B120" s="40" t="s">
+      <c r="B120" s="30" t="s">
         <v>306</v>
       </c>
       <c r="C120" s="17" t="s">
@@ -5594,7 +5594,7 @@
         <v>2</v>
       </c>
       <c r="E120" s="16"/>
-      <c r="F120" s="29"/>
+      <c r="F120" s="34"/>
       <c r="G120" s="23" t="s">
         <v>91</v>
       </c>
@@ -5609,7 +5609,7 @@
       <c r="A121" s="16">
         <v>109</v>
       </c>
-      <c r="B121" s="40" t="s">
+      <c r="B121" s="30" t="s">
         <v>307</v>
       </c>
       <c r="C121" s="17" t="s">
@@ -5619,7 +5619,7 @@
         <v>3</v>
       </c>
       <c r="E121" s="16"/>
-      <c r="F121" s="29"/>
+      <c r="F121" s="34"/>
       <c r="G121" s="23" t="s">
         <v>91</v>
       </c>
@@ -5634,7 +5634,7 @@
       <c r="A122" s="16">
         <v>110</v>
       </c>
-      <c r="B122" s="40" t="s">
+      <c r="B122" s="30" t="s">
         <v>127</v>
       </c>
       <c r="C122" s="17" t="s">
@@ -5644,7 +5644,7 @@
         <v>3</v>
       </c>
       <c r="E122" s="16"/>
-      <c r="F122" s="29"/>
+      <c r="F122" s="34"/>
       <c r="G122" s="4"/>
       <c r="H122" s="23"/>
       <c r="I122" t="s">
@@ -5657,7 +5657,7 @@
       <c r="A123" s="16">
         <v>111</v>
       </c>
-      <c r="B123" s="40" t="s">
+      <c r="B123" s="30" t="s">
         <v>126</v>
       </c>
       <c r="C123" s="17" t="s">
@@ -5667,7 +5667,7 @@
         <v>3</v>
       </c>
       <c r="E123" s="16"/>
-      <c r="F123" s="29"/>
+      <c r="F123" s="34"/>
       <c r="G123" s="4"/>
       <c r="H123" s="23"/>
       <c r="I123" t="s">
@@ -5680,7 +5680,7 @@
       <c r="A124" s="16">
         <v>112</v>
       </c>
-      <c r="B124" s="40" t="s">
+      <c r="B124" s="30" t="s">
         <v>110</v>
       </c>
       <c r="C124" s="17" t="s">
@@ -5690,7 +5690,7 @@
         <v>3</v>
       </c>
       <c r="E124" s="16"/>
-      <c r="F124" s="29"/>
+      <c r="F124" s="34"/>
       <c r="G124" s="4"/>
       <c r="H124" s="23"/>
       <c r="I124" t="s">
@@ -5703,7 +5703,7 @@
       <c r="A125" s="16">
         <v>113</v>
       </c>
-      <c r="B125" s="40" t="s">
+      <c r="B125" s="30" t="s">
         <v>308</v>
       </c>
       <c r="C125" s="17" t="s">
@@ -5713,7 +5713,7 @@
         <v>3</v>
       </c>
       <c r="E125" s="16"/>
-      <c r="F125" s="29"/>
+      <c r="F125" s="34"/>
       <c r="G125" s="23" t="s">
         <v>91</v>
       </c>
@@ -5728,7 +5728,7 @@
       <c r="A126" s="16">
         <v>114</v>
       </c>
-      <c r="B126" s="40" t="s">
+      <c r="B126" s="30" t="s">
         <v>309</v>
       </c>
       <c r="C126" s="17" t="s">
@@ -5738,7 +5738,7 @@
         <v>3</v>
       </c>
       <c r="E126" s="16"/>
-      <c r="F126" s="29"/>
+      <c r="F126" s="34"/>
       <c r="G126" s="23" t="s">
         <v>13</v>
       </c>
@@ -5753,7 +5753,7 @@
       <c r="A127" s="16">
         <v>115</v>
       </c>
-      <c r="B127" s="40" t="s">
+      <c r="B127" s="30" t="s">
         <v>310</v>
       </c>
       <c r="C127" s="17" t="s">
@@ -5763,7 +5763,7 @@
         <v>3</v>
       </c>
       <c r="E127" s="16"/>
-      <c r="F127" s="29"/>
+      <c r="F127" s="34"/>
       <c r="G127" s="23" t="s">
         <v>363</v>
       </c>
@@ -5778,7 +5778,7 @@
       <c r="A128" s="16">
         <v>116</v>
       </c>
-      <c r="B128" s="40" t="s">
+      <c r="B128" s="30" t="s">
         <v>311</v>
       </c>
       <c r="C128" s="17" t="s">
@@ -5788,7 +5788,7 @@
         <v>3</v>
       </c>
       <c r="E128" s="16"/>
-      <c r="F128" s="29"/>
+      <c r="F128" s="34"/>
       <c r="G128" s="23" t="s">
         <v>363</v>
       </c>
@@ -5803,7 +5803,7 @@
       <c r="A129" s="16">
         <v>117</v>
       </c>
-      <c r="B129" s="40" t="s">
+      <c r="B129" s="30" t="s">
         <v>312</v>
       </c>
       <c r="C129" s="17" t="s">
@@ -5813,7 +5813,7 @@
         <v>3</v>
       </c>
       <c r="E129" s="16"/>
-      <c r="F129" s="29"/>
+      <c r="F129" s="34"/>
       <c r="G129" s="23" t="s">
         <v>282</v>
       </c>
@@ -5828,7 +5828,7 @@
       <c r="A130" s="16">
         <v>118</v>
       </c>
-      <c r="B130" s="40" t="s">
+      <c r="B130" s="30" t="s">
         <v>313</v>
       </c>
       <c r="C130" s="17" t="s">
@@ -5838,7 +5838,7 @@
         <v>3</v>
       </c>
       <c r="E130" s="16"/>
-      <c r="F130" s="29"/>
+      <c r="F130" s="34"/>
       <c r="G130" s="4"/>
       <c r="H130" s="23"/>
       <c r="I130" t="s">
@@ -5851,7 +5851,7 @@
       <c r="A131" s="16">
         <v>119</v>
       </c>
-      <c r="B131" s="40" t="s">
+      <c r="B131" s="30" t="s">
         <v>314</v>
       </c>
       <c r="C131" s="17" t="s">
@@ -5861,7 +5861,7 @@
         <v>3</v>
       </c>
       <c r="E131" s="16"/>
-      <c r="F131" s="29"/>
+      <c r="F131" s="34"/>
       <c r="G131" s="23" t="s">
         <v>92</v>
       </c>
@@ -5876,7 +5876,7 @@
       <c r="A132" s="16">
         <v>120</v>
       </c>
-      <c r="B132" s="40" t="s">
+      <c r="B132" s="30" t="s">
         <v>315</v>
       </c>
       <c r="C132" s="17" t="s">
@@ -5886,7 +5886,7 @@
         <v>3</v>
       </c>
       <c r="E132" s="16"/>
-      <c r="F132" s="29"/>
+      <c r="F132" s="34"/>
       <c r="G132" s="4"/>
       <c r="H132" s="23"/>
       <c r="I132" t="s">
@@ -5899,7 +5899,7 @@
       <c r="A133" s="16">
         <v>121</v>
       </c>
-      <c r="B133" s="40" t="s">
+      <c r="B133" s="30" t="s">
         <v>316</v>
       </c>
       <c r="C133" s="17" t="s">
@@ -5909,7 +5909,7 @@
         <v>3</v>
       </c>
       <c r="E133" s="16"/>
-      <c r="F133" s="29"/>
+      <c r="F133" s="34"/>
       <c r="G133" s="4"/>
       <c r="H133" s="23"/>
       <c r="I133" t="s">
@@ -5919,34 +5919,34 @@
       <c r="K133" s="4"/>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A134" s="30" t="s">
+      <c r="A134" s="32" t="s">
         <v>354</v>
       </c>
-      <c r="B134" s="30"/>
-      <c r="C134" s="30"/>
-      <c r="D134" s="30"/>
-      <c r="E134" s="30"/>
-      <c r="F134" s="30"/>
-      <c r="G134" s="30"/>
-      <c r="H134" s="30"/>
-      <c r="I134" s="30"/>
-      <c r="J134" s="30"/>
-      <c r="K134" s="30"/>
+      <c r="B134" s="32"/>
+      <c r="C134" s="32"/>
+      <c r="D134" s="32"/>
+      <c r="E134" s="32"/>
+      <c r="F134" s="32"/>
+      <c r="G134" s="32"/>
+      <c r="H134" s="32"/>
+      <c r="I134" s="32"/>
+      <c r="J134" s="32"/>
+      <c r="K134" s="32"/>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A135" s="30" t="s">
+      <c r="A135" s="32" t="s">
         <v>355</v>
       </c>
-      <c r="B135" s="30"/>
-      <c r="C135" s="30"/>
-      <c r="D135" s="30"/>
-      <c r="E135" s="30"/>
-      <c r="F135" s="30"/>
-      <c r="G135" s="30"/>
-      <c r="H135" s="30"/>
-      <c r="I135" s="30"/>
-      <c r="J135" s="30"/>
-      <c r="K135" s="30"/>
+      <c r="B135" s="32"/>
+      <c r="C135" s="32"/>
+      <c r="D135" s="32"/>
+      <c r="E135" s="32"/>
+      <c r="F135" s="32"/>
+      <c r="G135" s="32"/>
+      <c r="H135" s="32"/>
+      <c r="I135" s="32"/>
+      <c r="J135" s="32"/>
+      <c r="K135" s="32"/>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="16"/>
@@ -5962,19 +5962,19 @@
       <c r="K136" s="4"/>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A137" s="31" t="s">
+      <c r="A137" s="33" t="s">
         <v>277</v>
       </c>
-      <c r="B137" s="31"/>
-      <c r="C137" s="31"/>
-      <c r="D137" s="31"/>
-      <c r="E137" s="31"/>
-      <c r="F137" s="31"/>
-      <c r="G137" s="31"/>
-      <c r="H137" s="31"/>
-      <c r="I137" s="31"/>
-      <c r="J137" s="31"/>
-      <c r="K137" s="31"/>
+      <c r="B137" s="33"/>
+      <c r="C137" s="33"/>
+      <c r="D137" s="33"/>
+      <c r="E137" s="33"/>
+      <c r="F137" s="33"/>
+      <c r="G137" s="33"/>
+      <c r="H137" s="33"/>
+      <c r="I137" s="33"/>
+      <c r="J137" s="33"/>
+      <c r="K137" s="33"/>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="16">
@@ -6240,7 +6240,7 @@
       <c r="A148" s="16">
         <v>132</v>
       </c>
-      <c r="B148" s="40" t="s">
+      <c r="B148" s="30" t="s">
         <v>285</v>
       </c>
       <c r="C148" s="17" t="s">
@@ -6249,10 +6249,10 @@
       <c r="D148" s="16">
         <v>3</v>
       </c>
-      <c r="E148" s="29" t="s">
+      <c r="E148" s="34" t="s">
         <v>198</v>
       </c>
-      <c r="F148" s="29" t="s">
+      <c r="F148" s="34" t="s">
         <v>400</v>
       </c>
       <c r="G148" s="4"/>
@@ -6267,7 +6267,7 @@
       <c r="A149" s="16">
         <v>133</v>
       </c>
-      <c r="B149" s="40" t="s">
+      <c r="B149" s="30" t="s">
         <v>287</v>
       </c>
       <c r="C149" s="17" t="s">
@@ -6276,8 +6276,8 @@
       <c r="D149" s="16">
         <v>3</v>
       </c>
-      <c r="E149" s="29"/>
-      <c r="F149" s="29"/>
+      <c r="E149" s="34"/>
+      <c r="F149" s="34"/>
       <c r="G149" s="4"/>
       <c r="H149" s="23"/>
       <c r="I149" t="s">
@@ -6290,7 +6290,7 @@
       <c r="A150" s="16">
         <v>134</v>
       </c>
-      <c r="B150" s="40" t="s">
+      <c r="B150" s="30" t="s">
         <v>116</v>
       </c>
       <c r="C150" s="17" t="s">
@@ -6299,10 +6299,10 @@
       <c r="D150" s="16">
         <v>3</v>
       </c>
-      <c r="E150" s="29" t="s">
+      <c r="E150" s="34" t="s">
         <v>199</v>
       </c>
-      <c r="F150" s="29"/>
+      <c r="F150" s="34"/>
       <c r="G150" s="4"/>
       <c r="H150" s="23"/>
       <c r="I150" t="s">
@@ -6315,7 +6315,7 @@
       <c r="A151" s="16">
         <v>135</v>
       </c>
-      <c r="B151" s="40" t="s">
+      <c r="B151" s="30" t="s">
         <v>369</v>
       </c>
       <c r="C151" s="17" t="s">
@@ -6324,8 +6324,8 @@
       <c r="D151" s="16">
         <v>3</v>
       </c>
-      <c r="E151" s="29"/>
-      <c r="F151" s="29"/>
+      <c r="E151" s="34"/>
+      <c r="F151" s="34"/>
       <c r="G151" s="4"/>
       <c r="H151" s="23"/>
       <c r="I151" t="s">
@@ -6338,7 +6338,7 @@
       <c r="A152" s="16">
         <v>136</v>
       </c>
-      <c r="B152" s="40" t="s">
+      <c r="B152" s="30" t="s">
         <v>370</v>
       </c>
       <c r="C152" s="17" t="s">
@@ -6347,10 +6347,10 @@
       <c r="D152" s="16">
         <v>3</v>
       </c>
-      <c r="E152" s="29" t="s">
+      <c r="E152" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="F152" s="29"/>
+      <c r="F152" s="34"/>
       <c r="G152" s="4"/>
       <c r="H152" s="23"/>
       <c r="I152" t="s">
@@ -6363,7 +6363,7 @@
       <c r="A153" s="16">
         <v>137</v>
       </c>
-      <c r="B153" s="40" t="s">
+      <c r="B153" s="30" t="s">
         <v>296</v>
       </c>
       <c r="C153" s="17" t="s">
@@ -6372,8 +6372,8 @@
       <c r="D153" s="16">
         <v>3</v>
       </c>
-      <c r="E153" s="29"/>
-      <c r="F153" s="29"/>
+      <c r="E153" s="34"/>
+      <c r="F153" s="34"/>
       <c r="G153" s="4"/>
       <c r="H153" s="23"/>
       <c r="I153" t="s">
@@ -6440,7 +6440,7 @@
       <c r="A156" s="16">
         <v>140</v>
       </c>
-      <c r="B156" s="40" t="s">
+      <c r="B156" s="30" t="s">
         <v>373</v>
       </c>
       <c r="C156" s="17" t="s">
@@ -6450,7 +6450,7 @@
         <v>15</v>
       </c>
       <c r="E156" s="16"/>
-      <c r="F156" s="29">
+      <c r="F156" s="34">
         <v>15</v>
       </c>
       <c r="G156" s="4" t="s">
@@ -6467,7 +6467,7 @@
       <c r="A157" s="16">
         <v>141</v>
       </c>
-      <c r="B157" s="40" t="s">
+      <c r="B157" s="30" t="s">
         <v>374</v>
       </c>
       <c r="C157" s="17" t="s">
@@ -6477,7 +6477,7 @@
         <v>6</v>
       </c>
       <c r="E157" s="16"/>
-      <c r="F157" s="29"/>
+      <c r="F157" s="34"/>
       <c r="G157" s="4" t="s">
         <v>207</v>
       </c>
@@ -6492,7 +6492,7 @@
       <c r="A158" s="16">
         <v>142</v>
       </c>
-      <c r="B158" s="40" t="s">
+      <c r="B158" s="30" t="s">
         <v>375</v>
       </c>
       <c r="C158" s="17" t="s">
@@ -6502,7 +6502,7 @@
         <v>3</v>
       </c>
       <c r="E158" s="16"/>
-      <c r="F158" s="29"/>
+      <c r="F158" s="34"/>
       <c r="G158" s="4"/>
       <c r="H158" s="23"/>
       <c r="I158" t="s">
@@ -6515,7 +6515,7 @@
       <c r="A159" s="16">
         <v>143</v>
       </c>
-      <c r="B159" s="40" t="s">
+      <c r="B159" s="30" t="s">
         <v>376</v>
       </c>
       <c r="C159" s="17" t="s">
@@ -6525,7 +6525,7 @@
         <v>3</v>
       </c>
       <c r="E159" s="16"/>
-      <c r="F159" s="29"/>
+      <c r="F159" s="34"/>
       <c r="G159" s="4"/>
       <c r="H159" s="23"/>
       <c r="I159" t="s">
@@ -6538,7 +6538,7 @@
       <c r="A160" s="16">
         <v>144</v>
       </c>
-      <c r="B160" s="40" t="s">
+      <c r="B160" s="30" t="s">
         <v>127</v>
       </c>
       <c r="C160" s="17" t="s">
@@ -6548,7 +6548,7 @@
         <v>3</v>
       </c>
       <c r="E160" s="16"/>
-      <c r="F160" s="29"/>
+      <c r="F160" s="34"/>
       <c r="G160" s="4"/>
       <c r="H160" s="23"/>
       <c r="I160" t="s">
@@ -6561,7 +6561,7 @@
       <c r="A161" s="16">
         <v>145</v>
       </c>
-      <c r="B161" s="40" t="s">
+      <c r="B161" s="30" t="s">
         <v>314</v>
       </c>
       <c r="C161" s="17" t="s">
@@ -6571,7 +6571,7 @@
         <v>3</v>
       </c>
       <c r="E161" s="16"/>
-      <c r="F161" s="29"/>
+      <c r="F161" s="34"/>
       <c r="G161" s="4"/>
       <c r="H161" s="23"/>
       <c r="I161" t="s">
@@ -6584,7 +6584,7 @@
       <c r="A162" s="16">
         <v>146</v>
       </c>
-      <c r="B162" s="40" t="s">
+      <c r="B162" s="30" t="s">
         <v>377</v>
       </c>
       <c r="C162" s="17" t="s">
@@ -6594,7 +6594,7 @@
         <v>3</v>
       </c>
       <c r="E162" s="16"/>
-      <c r="F162" s="29"/>
+      <c r="F162" s="34"/>
       <c r="G162" s="4"/>
       <c r="H162" s="23"/>
       <c r="I162" t="s">
@@ -6607,7 +6607,7 @@
       <c r="A163" s="16">
         <v>147</v>
       </c>
-      <c r="B163" s="40" t="s">
+      <c r="B163" s="30" t="s">
         <v>378</v>
       </c>
       <c r="C163" s="17" t="s">
@@ -6617,7 +6617,7 @@
         <v>3</v>
       </c>
       <c r="E163" s="16"/>
-      <c r="F163" s="29"/>
+      <c r="F163" s="34"/>
       <c r="G163" s="4"/>
       <c r="H163" s="23"/>
       <c r="I163" t="s">
@@ -6630,7 +6630,7 @@
       <c r="A164" s="16">
         <v>148</v>
       </c>
-      <c r="B164" s="40" t="s">
+      <c r="B164" s="30" t="s">
         <v>379</v>
       </c>
       <c r="C164" s="17" t="s">
@@ -6640,7 +6640,7 @@
         <v>3</v>
       </c>
       <c r="E164" s="16"/>
-      <c r="F164" s="29"/>
+      <c r="F164" s="34"/>
       <c r="G164" s="4"/>
       <c r="H164" s="23"/>
       <c r="I164" t="s">
@@ -6650,34 +6650,34 @@
       <c r="K164" s="4"/>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A165" s="30" t="s">
+      <c r="A165" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="B165" s="30"/>
-      <c r="C165" s="30"/>
-      <c r="D165" s="30"/>
-      <c r="E165" s="30"/>
-      <c r="F165" s="30"/>
-      <c r="G165" s="30"/>
-      <c r="H165" s="30"/>
-      <c r="I165" s="30"/>
-      <c r="J165" s="30"/>
-      <c r="K165" s="30"/>
+      <c r="B165" s="32"/>
+      <c r="C165" s="32"/>
+      <c r="D165" s="32"/>
+      <c r="E165" s="32"/>
+      <c r="F165" s="32"/>
+      <c r="G165" s="32"/>
+      <c r="H165" s="32"/>
+      <c r="I165" s="32"/>
+      <c r="J165" s="32"/>
+      <c r="K165" s="32"/>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A166" s="30" t="s">
+      <c r="A166" s="32" t="s">
         <v>202</v>
       </c>
-      <c r="B166" s="30"/>
-      <c r="C166" s="30"/>
-      <c r="D166" s="30"/>
-      <c r="E166" s="30"/>
-      <c r="F166" s="30"/>
-      <c r="G166" s="30"/>
-      <c r="H166" s="30"/>
-      <c r="I166" s="30"/>
-      <c r="J166" s="30"/>
-      <c r="K166" s="30"/>
+      <c r="B166" s="32"/>
+      <c r="C166" s="32"/>
+      <c r="D166" s="32"/>
+      <c r="E166" s="32"/>
+      <c r="F166" s="32"/>
+      <c r="G166" s="32"/>
+      <c r="H166" s="32"/>
+      <c r="I166" s="32"/>
+      <c r="J166" s="32"/>
+      <c r="K166" s="32"/>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167" s="16"/>
@@ -6693,19 +6693,19 @@
       <c r="K167" s="4"/>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A168" s="31" t="s">
+      <c r="A168" s="33" t="s">
         <v>278</v>
       </c>
-      <c r="B168" s="31"/>
-      <c r="C168" s="31"/>
-      <c r="D168" s="31"/>
-      <c r="E168" s="31"/>
-      <c r="F168" s="31"/>
-      <c r="G168" s="31"/>
-      <c r="H168" s="31"/>
-      <c r="I168" s="31"/>
-      <c r="J168" s="31"/>
-      <c r="K168" s="31"/>
+      <c r="B168" s="33"/>
+      <c r="C168" s="33"/>
+      <c r="D168" s="33"/>
+      <c r="E168" s="33"/>
+      <c r="F168" s="33"/>
+      <c r="G168" s="33"/>
+      <c r="H168" s="33"/>
+      <c r="I168" s="33"/>
+      <c r="J168" s="33"/>
+      <c r="K168" s="33"/>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" s="16">
@@ -6954,7 +6954,7 @@
       <c r="A178" s="16">
         <v>158</v>
       </c>
-      <c r="B178" s="40" t="s">
+      <c r="B178" s="30" t="s">
         <v>588</v>
       </c>
       <c r="C178" s="17" t="s">
@@ -6964,7 +6964,7 @@
         <v>3</v>
       </c>
       <c r="E178" s="16"/>
-      <c r="F178" s="29">
+      <c r="F178" s="34">
         <v>9</v>
       </c>
       <c r="G178" s="23" t="s">
@@ -6981,7 +6981,7 @@
       <c r="A179" s="16">
         <v>159</v>
       </c>
-      <c r="B179" s="40" t="s">
+      <c r="B179" s="30" t="s">
         <v>128</v>
       </c>
       <c r="C179" s="17" t="s">
@@ -6991,7 +6991,7 @@
         <v>3</v>
       </c>
       <c r="E179" s="16"/>
-      <c r="F179" s="29"/>
+      <c r="F179" s="34"/>
       <c r="G179" s="23" t="s">
         <v>93</v>
       </c>
@@ -7006,7 +7006,7 @@
       <c r="A180" s="16">
         <v>160</v>
       </c>
-      <c r="B180" s="40" t="s">
+      <c r="B180" s="30" t="s">
         <v>410</v>
       </c>
       <c r="C180" s="17" t="s">
@@ -7016,7 +7016,7 @@
         <v>3</v>
       </c>
       <c r="E180" s="16"/>
-      <c r="F180" s="29"/>
+      <c r="F180" s="34"/>
       <c r="G180" s="23" t="s">
         <v>93</v>
       </c>
@@ -7031,7 +7031,7 @@
       <c r="A181" s="16">
         <v>161</v>
       </c>
-      <c r="B181" s="40" t="s">
+      <c r="B181" s="30" t="s">
         <v>411</v>
       </c>
       <c r="C181" s="17" t="s">
@@ -7041,7 +7041,7 @@
         <v>3</v>
       </c>
       <c r="E181" s="16"/>
-      <c r="F181" s="29"/>
+      <c r="F181" s="34"/>
       <c r="G181" s="4" t="s">
         <v>13</v>
       </c>
@@ -7056,7 +7056,7 @@
       <c r="A182" s="16">
         <v>162</v>
       </c>
-      <c r="B182" s="40" t="s">
+      <c r="B182" s="30" t="s">
         <v>412</v>
       </c>
       <c r="C182" s="17" t="s">
@@ -7066,7 +7066,7 @@
         <v>3</v>
       </c>
       <c r="E182" s="16"/>
-      <c r="F182" s="29"/>
+      <c r="F182" s="34"/>
       <c r="G182" s="23" t="s">
         <v>93</v>
       </c>
@@ -7081,7 +7081,7 @@
       <c r="A183" s="16">
         <v>163</v>
       </c>
-      <c r="B183" s="40" t="s">
+      <c r="B183" s="30" t="s">
         <v>130</v>
       </c>
       <c r="C183" s="17" t="s">
@@ -7091,7 +7091,7 @@
         <v>3</v>
       </c>
       <c r="E183" s="16"/>
-      <c r="F183" s="29"/>
+      <c r="F183" s="34"/>
       <c r="G183" s="23" t="s">
         <v>93</v>
       </c>
@@ -7160,7 +7160,7 @@
       <c r="A186" s="16">
         <v>166</v>
       </c>
-      <c r="B186" s="40" t="s">
+      <c r="B186" s="30" t="s">
         <v>415</v>
       </c>
       <c r="C186" s="17" t="s">
@@ -7170,7 +7170,7 @@
         <v>15</v>
       </c>
       <c r="E186" s="16"/>
-      <c r="F186" s="29">
+      <c r="F186" s="34">
         <v>15</v>
       </c>
       <c r="G186" s="23" t="s">
@@ -7187,7 +7187,7 @@
       <c r="A187" s="16">
         <v>167</v>
       </c>
-      <c r="B187" s="40" t="s">
+      <c r="B187" s="30" t="s">
         <v>416</v>
       </c>
       <c r="C187" s="17" t="s">
@@ -7197,7 +7197,7 @@
         <v>6</v>
       </c>
       <c r="E187" s="16"/>
-      <c r="F187" s="29"/>
+      <c r="F187" s="34"/>
       <c r="G187" s="23" t="s">
         <v>443</v>
       </c>
@@ -7212,7 +7212,7 @@
       <c r="A188" s="16">
         <v>168</v>
       </c>
-      <c r="B188" s="40" t="s">
+      <c r="B188" s="30" t="s">
         <v>126</v>
       </c>
       <c r="C188" s="17" t="s">
@@ -7222,7 +7222,7 @@
         <v>3</v>
       </c>
       <c r="E188" s="16"/>
-      <c r="F188" s="29"/>
+      <c r="F188" s="34"/>
       <c r="G188" s="23" t="s">
         <v>92</v>
       </c>
@@ -7237,7 +7237,7 @@
       <c r="A189" s="16">
         <v>169</v>
       </c>
-      <c r="B189" s="40" t="s">
+      <c r="B189" s="30" t="s">
         <v>417</v>
       </c>
       <c r="C189" s="17" t="s">
@@ -7247,7 +7247,7 @@
         <v>3</v>
       </c>
       <c r="E189" s="16"/>
-      <c r="F189" s="29"/>
+      <c r="F189" s="34"/>
       <c r="G189" s="23" t="s">
         <v>13</v>
       </c>
@@ -7262,7 +7262,7 @@
       <c r="A190" s="16">
         <v>170</v>
       </c>
-      <c r="B190" s="40" t="s">
+      <c r="B190" s="30" t="s">
         <v>418</v>
       </c>
       <c r="C190" s="17" t="s">
@@ -7272,7 +7272,7 @@
         <v>3</v>
       </c>
       <c r="E190" s="16"/>
-      <c r="F190" s="29"/>
+      <c r="F190" s="34"/>
       <c r="G190" s="23" t="s">
         <v>91</v>
       </c>
@@ -7287,7 +7287,7 @@
       <c r="A191" s="16">
         <v>171</v>
       </c>
-      <c r="B191" s="40" t="s">
+      <c r="B191" s="30" t="s">
         <v>419</v>
       </c>
       <c r="C191" s="17" t="s">
@@ -7297,7 +7297,7 @@
         <v>3</v>
       </c>
       <c r="E191" s="16"/>
-      <c r="F191" s="29"/>
+      <c r="F191" s="34"/>
       <c r="G191" s="23" t="s">
         <v>93</v>
       </c>
@@ -7312,7 +7312,7 @@
       <c r="A192" s="16">
         <v>172</v>
       </c>
-      <c r="B192" s="40" t="s">
+      <c r="B192" s="30" t="s">
         <v>420</v>
       </c>
       <c r="C192" s="17" t="s">
@@ -7322,7 +7322,7 @@
         <v>3</v>
       </c>
       <c r="E192" s="16"/>
-      <c r="F192" s="29"/>
+      <c r="F192" s="34"/>
       <c r="G192" s="23" t="s">
         <v>13</v>
       </c>
@@ -7337,7 +7337,7 @@
       <c r="A193" s="16">
         <v>173</v>
       </c>
-      <c r="B193" s="40" t="s">
+      <c r="B193" s="30" t="s">
         <v>421</v>
       </c>
       <c r="C193" s="17" t="s">
@@ -7347,7 +7347,7 @@
         <v>3</v>
       </c>
       <c r="E193" s="16"/>
-      <c r="F193" s="29"/>
+      <c r="F193" s="34"/>
       <c r="G193" s="23" t="s">
         <v>97</v>
       </c>
@@ -7362,7 +7362,7 @@
       <c r="A194" s="16">
         <v>174</v>
       </c>
-      <c r="B194" s="40" t="s">
+      <c r="B194" s="30" t="s">
         <v>125</v>
       </c>
       <c r="C194" s="17" t="s">
@@ -7372,7 +7372,7 @@
         <v>3</v>
       </c>
       <c r="E194" s="16"/>
-      <c r="F194" s="29"/>
+      <c r="F194" s="34"/>
       <c r="G194" s="23" t="s">
         <v>93</v>
       </c>
@@ -7387,7 +7387,7 @@
       <c r="A195" s="16">
         <v>175</v>
       </c>
-      <c r="B195" s="40" t="s">
+      <c r="B195" s="30" t="s">
         <v>422</v>
       </c>
       <c r="C195" s="17" t="s">
@@ -7397,7 +7397,7 @@
         <v>3</v>
       </c>
       <c r="E195" s="16"/>
-      <c r="F195" s="29"/>
+      <c r="F195" s="34"/>
       <c r="G195" s="23" t="s">
         <v>13</v>
       </c>
@@ -7409,34 +7409,34 @@
       <c r="K195" s="4"/>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A196" s="30" t="s">
+      <c r="A196" s="32" t="s">
         <v>444</v>
       </c>
-      <c r="B196" s="30"/>
-      <c r="C196" s="30"/>
-      <c r="D196" s="30"/>
-      <c r="E196" s="30"/>
-      <c r="F196" s="30"/>
-      <c r="G196" s="30"/>
-      <c r="H196" s="30"/>
-      <c r="I196" s="30"/>
-      <c r="J196" s="30"/>
-      <c r="K196" s="30"/>
+      <c r="B196" s="32"/>
+      <c r="C196" s="32"/>
+      <c r="D196" s="32"/>
+      <c r="E196" s="32"/>
+      <c r="F196" s="32"/>
+      <c r="G196" s="32"/>
+      <c r="H196" s="32"/>
+      <c r="I196" s="32"/>
+      <c r="J196" s="32"/>
+      <c r="K196" s="32"/>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A197" s="30" t="s">
+      <c r="A197" s="32" t="s">
         <v>445</v>
       </c>
-      <c r="B197" s="30"/>
-      <c r="C197" s="30"/>
-      <c r="D197" s="30"/>
-      <c r="E197" s="30"/>
-      <c r="F197" s="30"/>
-      <c r="G197" s="30"/>
-      <c r="H197" s="30"/>
-      <c r="I197" s="30"/>
-      <c r="J197" s="30"/>
-      <c r="K197" s="30"/>
+      <c r="B197" s="32"/>
+      <c r="C197" s="32"/>
+      <c r="D197" s="32"/>
+      <c r="E197" s="32"/>
+      <c r="F197" s="32"/>
+      <c r="G197" s="32"/>
+      <c r="H197" s="32"/>
+      <c r="I197" s="32"/>
+      <c r="J197" s="32"/>
+      <c r="K197" s="32"/>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198" s="16"/>
@@ -7452,19 +7452,19 @@
       <c r="K198" s="4"/>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A199" s="31" t="s">
+      <c r="A199" s="33" t="s">
         <v>279</v>
       </c>
-      <c r="B199" s="31"/>
-      <c r="C199" s="31"/>
-      <c r="D199" s="31"/>
-      <c r="E199" s="31"/>
-      <c r="F199" s="31"/>
-      <c r="G199" s="31"/>
-      <c r="H199" s="31"/>
-      <c r="I199" s="31"/>
-      <c r="J199" s="31"/>
-      <c r="K199" s="31"/>
+      <c r="B199" s="33"/>
+      <c r="C199" s="33"/>
+      <c r="D199" s="33"/>
+      <c r="E199" s="33"/>
+      <c r="F199" s="33"/>
+      <c r="G199" s="33"/>
+      <c r="H199" s="33"/>
+      <c r="I199" s="33"/>
+      <c r="J199" s="33"/>
+      <c r="K199" s="33"/>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" s="16">
@@ -7497,7 +7497,7 @@
       <c r="A201" s="16">
         <v>177</v>
       </c>
-      <c r="B201" s="40" t="s">
+      <c r="B201" s="30" t="s">
         <v>447</v>
       </c>
       <c r="C201" s="17" t="s">
@@ -7507,7 +7507,7 @@
         <v>3</v>
       </c>
       <c r="E201" s="16"/>
-      <c r="F201" s="29">
+      <c r="F201" s="34">
         <v>3</v>
       </c>
       <c r="G201" s="4"/>
@@ -7522,7 +7522,7 @@
       <c r="A202" s="16">
         <v>178</v>
       </c>
-      <c r="B202" s="40" t="s">
+      <c r="B202" s="30" t="s">
         <v>448</v>
       </c>
       <c r="C202" s="17" t="s">
@@ -7532,7 +7532,7 @@
         <v>3</v>
       </c>
       <c r="E202" s="16"/>
-      <c r="F202" s="29"/>
+      <c r="F202" s="34"/>
       <c r="G202" s="4"/>
       <c r="H202" s="23"/>
       <c r="I202" t="s">
@@ -7545,7 +7545,7 @@
       <c r="A203" s="16">
         <v>179</v>
       </c>
-      <c r="B203" s="40" t="s">
+      <c r="B203" s="30" t="s">
         <v>449</v>
       </c>
       <c r="C203" s="17" t="s">
@@ -7555,7 +7555,7 @@
         <v>3</v>
       </c>
       <c r="E203" s="16"/>
-      <c r="F203" s="29"/>
+      <c r="F203" s="34"/>
       <c r="G203" s="4"/>
       <c r="H203" s="23"/>
       <c r="I203" t="s">
@@ -7722,7 +7722,7 @@
       <c r="A210" s="16">
         <v>186</v>
       </c>
-      <c r="B210" s="40" t="s">
+      <c r="B210" s="30" t="s">
         <v>453</v>
       </c>
       <c r="C210" s="17" t="s">
@@ -7732,7 +7732,7 @@
         <v>3</v>
       </c>
       <c r="E210" s="16"/>
-      <c r="F210" s="29">
+      <c r="F210" s="34">
         <v>3</v>
       </c>
       <c r="G210" s="4"/>
@@ -7747,7 +7747,7 @@
       <c r="A211" s="16">
         <v>187</v>
       </c>
-      <c r="B211" s="40" t="s">
+      <c r="B211" s="30" t="s">
         <v>126</v>
       </c>
       <c r="C211" s="17" t="s">
@@ -7757,7 +7757,7 @@
         <v>3</v>
       </c>
       <c r="E211" s="16"/>
-      <c r="F211" s="29"/>
+      <c r="F211" s="34"/>
       <c r="G211" s="4" t="s">
         <v>9</v>
       </c>
@@ -7772,7 +7772,7 @@
       <c r="A212" s="16">
         <v>188</v>
       </c>
-      <c r="B212" s="40" t="s">
+      <c r="B212" s="30" t="s">
         <v>116</v>
       </c>
       <c r="C212" s="17" t="s">
@@ -7782,7 +7782,7 @@
         <v>3</v>
       </c>
       <c r="E212" s="16"/>
-      <c r="F212" s="29"/>
+      <c r="F212" s="34"/>
       <c r="G212" s="4"/>
       <c r="H212" s="23"/>
       <c r="I212" t="s">
@@ -7795,7 +7795,7 @@
       <c r="A213" s="16">
         <v>189</v>
       </c>
-      <c r="B213" s="40" t="s">
+      <c r="B213" s="30" t="s">
         <v>282</v>
       </c>
       <c r="C213" s="17" t="s">
@@ -7805,7 +7805,7 @@
         <v>3</v>
       </c>
       <c r="E213" s="16"/>
-      <c r="F213" s="29"/>
+      <c r="F213" s="34"/>
       <c r="G213" s="4"/>
       <c r="H213" s="23"/>
       <c r="I213" t="s">
@@ -7845,7 +7845,7 @@
       <c r="A215" s="16">
         <v>191</v>
       </c>
-      <c r="B215" s="40" t="s">
+      <c r="B215" s="30" t="s">
         <v>455</v>
       </c>
       <c r="C215" s="17" t="s">
@@ -7854,10 +7854,10 @@
       <c r="D215" s="16">
         <v>3</v>
       </c>
-      <c r="E215" s="29" t="s">
+      <c r="E215" s="34" t="s">
         <v>198</v>
       </c>
-      <c r="F215" s="29" t="s">
+      <c r="F215" s="34" t="s">
         <v>492</v>
       </c>
       <c r="G215" s="23" t="s">
@@ -7874,7 +7874,7 @@
       <c r="A216" s="16">
         <v>192</v>
       </c>
-      <c r="B216" s="40" t="s">
+      <c r="B216" s="30" t="s">
         <v>456</v>
       </c>
       <c r="C216" s="15" t="s">
@@ -7883,8 +7883,8 @@
       <c r="D216" s="16">
         <v>3</v>
       </c>
-      <c r="E216" s="29"/>
-      <c r="F216" s="29"/>
+      <c r="E216" s="34"/>
+      <c r="F216" s="34"/>
       <c r="G216" s="23" t="s">
         <v>455</v>
       </c>
@@ -7899,7 +7899,7 @@
       <c r="A217" s="16">
         <v>193</v>
       </c>
-      <c r="B217" s="40" t="s">
+      <c r="B217" s="30" t="s">
         <v>457</v>
       </c>
       <c r="C217" s="17" t="s">
@@ -7908,8 +7908,8 @@
       <c r="D217" s="16">
         <v>3</v>
       </c>
-      <c r="E217" s="29"/>
-      <c r="F217" s="29"/>
+      <c r="E217" s="34"/>
+      <c r="F217" s="34"/>
       <c r="G217" s="23" t="s">
         <v>455</v>
       </c>
@@ -7924,7 +7924,7 @@
       <c r="A218" s="16">
         <v>194</v>
       </c>
-      <c r="B218" s="40" t="s">
+      <c r="B218" s="30" t="s">
         <v>377</v>
       </c>
       <c r="C218" s="17" t="s">
@@ -7933,8 +7933,8 @@
       <c r="D218" s="16">
         <v>3</v>
       </c>
-      <c r="E218" s="29"/>
-      <c r="F218" s="29"/>
+      <c r="E218" s="34"/>
+      <c r="F218" s="34"/>
       <c r="G218" s="23" t="s">
         <v>452</v>
       </c>
@@ -7949,7 +7949,7 @@
       <c r="A219" s="16">
         <v>195</v>
       </c>
-      <c r="B219" s="40" t="s">
+      <c r="B219" s="30" t="s">
         <v>379</v>
       </c>
       <c r="C219" s="17" t="s">
@@ -7958,10 +7958,10 @@
       <c r="D219" s="16">
         <v>3</v>
       </c>
-      <c r="E219" s="29" t="s">
+      <c r="E219" s="34" t="s">
         <v>199</v>
       </c>
-      <c r="F219" s="29"/>
+      <c r="F219" s="34"/>
       <c r="G219" s="4"/>
       <c r="H219" s="23"/>
       <c r="I219" t="s">
@@ -7974,7 +7974,7 @@
       <c r="A220" s="16">
         <v>196</v>
       </c>
-      <c r="B220" s="40" t="s">
+      <c r="B220" s="30" t="s">
         <v>124</v>
       </c>
       <c r="C220" s="17" t="s">
@@ -7983,8 +7983,8 @@
       <c r="D220" s="16">
         <v>3</v>
       </c>
-      <c r="E220" s="29"/>
-      <c r="F220" s="29"/>
+      <c r="E220" s="34"/>
+      <c r="F220" s="34"/>
       <c r="G220" s="23" t="s">
         <v>283</v>
       </c>
@@ -7999,7 +7999,7 @@
       <c r="A221" s="16">
         <v>197</v>
       </c>
-      <c r="B221" s="40" t="s">
+      <c r="B221" s="30" t="s">
         <v>458</v>
       </c>
       <c r="C221" s="17" t="s">
@@ -8008,8 +8008,8 @@
       <c r="D221" s="16">
         <v>3</v>
       </c>
-      <c r="E221" s="29"/>
-      <c r="F221" s="29"/>
+      <c r="E221" s="34"/>
+      <c r="F221" s="34"/>
       <c r="G221" s="23" t="s">
         <v>283</v>
       </c>
@@ -8024,7 +8024,7 @@
       <c r="A222" s="16">
         <v>198</v>
       </c>
-      <c r="B222" s="40" t="s">
+      <c r="B222" s="30" t="s">
         <v>459</v>
       </c>
       <c r="C222" s="17" t="s">
@@ -8033,8 +8033,8 @@
       <c r="D222" s="16">
         <v>3</v>
       </c>
-      <c r="E222" s="29"/>
-      <c r="F222" s="29"/>
+      <c r="E222" s="34"/>
+      <c r="F222" s="34"/>
       <c r="G222" s="4"/>
       <c r="H222" s="23"/>
       <c r="I222" t="s">
@@ -8047,7 +8047,7 @@
       <c r="A223" s="16">
         <v>199</v>
       </c>
-      <c r="B223" s="40" t="s">
+      <c r="B223" s="30" t="s">
         <v>378</v>
       </c>
       <c r="C223" s="17" t="s">
@@ -8056,8 +8056,8 @@
       <c r="D223" s="16">
         <v>3</v>
       </c>
-      <c r="E223" s="29"/>
-      <c r="F223" s="29"/>
+      <c r="E223" s="34"/>
+      <c r="F223" s="34"/>
       <c r="G223" s="4"/>
       <c r="H223" s="23"/>
       <c r="I223" t="s">
@@ -8097,7 +8097,7 @@
       <c r="A225" s="16">
         <v>201</v>
       </c>
-      <c r="B225" s="40" t="s">
+      <c r="B225" s="30" t="s">
         <v>461</v>
       </c>
       <c r="C225" s="17" t="s">
@@ -8107,7 +8107,7 @@
         <v>15</v>
       </c>
       <c r="E225" s="16"/>
-      <c r="F225" s="29">
+      <c r="F225" s="34">
         <v>15</v>
       </c>
       <c r="G225" s="4" t="s">
@@ -8124,7 +8124,7 @@
       <c r="A226" s="16">
         <v>202</v>
       </c>
-      <c r="B226" s="40" t="s">
+      <c r="B226" s="30" t="s">
         <v>462</v>
       </c>
       <c r="C226" s="17" t="s">
@@ -8134,7 +8134,7 @@
         <v>6</v>
       </c>
       <c r="E226" s="16"/>
-      <c r="F226" s="29"/>
+      <c r="F226" s="34"/>
       <c r="G226" s="4" t="s">
         <v>208</v>
       </c>
@@ -8149,7 +8149,7 @@
       <c r="A227" s="16">
         <v>203</v>
       </c>
-      <c r="B227" s="40" t="s">
+      <c r="B227" s="30" t="s">
         <v>463</v>
       </c>
       <c r="C227" s="17" t="s">
@@ -8159,7 +8159,7 @@
         <v>3</v>
       </c>
       <c r="E227" s="16"/>
-      <c r="F227" s="29"/>
+      <c r="F227" s="34"/>
       <c r="G227" s="4"/>
       <c r="H227" s="23"/>
       <c r="I227" t="s">
@@ -8172,7 +8172,7 @@
       <c r="A228" s="16">
         <v>204</v>
       </c>
-      <c r="B228" s="40" t="s">
+      <c r="B228" s="30" t="s">
         <v>464</v>
       </c>
       <c r="C228" s="17" t="s">
@@ -8182,7 +8182,7 @@
         <v>3</v>
       </c>
       <c r="E228" s="16"/>
-      <c r="F228" s="29"/>
+      <c r="F228" s="34"/>
       <c r="G228" s="23" t="s">
         <v>315</v>
       </c>
@@ -8197,7 +8197,7 @@
       <c r="A229" s="16">
         <v>205</v>
       </c>
-      <c r="B229" s="40" t="s">
+      <c r="B229" s="30" t="s">
         <v>294</v>
       </c>
       <c r="C229" s="17" t="s">
@@ -8207,7 +8207,7 @@
         <v>3</v>
       </c>
       <c r="E229" s="16"/>
-      <c r="F229" s="29"/>
+      <c r="F229" s="34"/>
       <c r="G229" s="23" t="s">
         <v>359</v>
       </c>
@@ -8222,7 +8222,7 @@
       <c r="A230" s="16">
         <v>206</v>
       </c>
-      <c r="B230" s="40" t="s">
+      <c r="B230" s="30" t="s">
         <v>368</v>
       </c>
       <c r="C230" s="17" t="s">
@@ -8232,7 +8232,7 @@
         <v>3</v>
       </c>
       <c r="E230" s="16"/>
-      <c r="F230" s="29"/>
+      <c r="F230" s="34"/>
       <c r="G230" s="4"/>
       <c r="H230" s="23"/>
       <c r="I230" t="s">
@@ -8245,7 +8245,7 @@
       <c r="A231" s="16">
         <v>207</v>
       </c>
-      <c r="B231" s="40" t="s">
+      <c r="B231" s="30" t="s">
         <v>366</v>
       </c>
       <c r="C231" s="17" t="s">
@@ -8255,7 +8255,7 @@
         <v>3</v>
       </c>
       <c r="E231" s="16"/>
-      <c r="F231" s="29"/>
+      <c r="F231" s="34"/>
       <c r="G231" s="4"/>
       <c r="H231" s="23"/>
       <c r="I231" t="s">
@@ -8268,7 +8268,7 @@
       <c r="A232" s="16">
         <v>208</v>
       </c>
-      <c r="B232" s="40" t="s">
+      <c r="B232" s="30" t="s">
         <v>295</v>
       </c>
       <c r="C232" s="17" t="s">
@@ -8278,7 +8278,7 @@
         <v>3</v>
       </c>
       <c r="E232" s="16"/>
-      <c r="F232" s="29"/>
+      <c r="F232" s="34"/>
       <c r="G232" s="23" t="s">
         <v>92</v>
       </c>
@@ -8293,7 +8293,7 @@
       <c r="A233" s="16">
         <v>209</v>
       </c>
-      <c r="B233" s="40" t="s">
+      <c r="B233" s="30" t="s">
         <v>465</v>
       </c>
       <c r="C233" s="17" t="s">
@@ -8303,7 +8303,7 @@
         <v>3</v>
       </c>
       <c r="E233" s="16"/>
-      <c r="F233" s="29"/>
+      <c r="F233" s="34"/>
       <c r="G233" s="4"/>
       <c r="H233" s="23"/>
       <c r="I233" t="s">
@@ -8316,7 +8316,7 @@
       <c r="A234" s="16">
         <v>210</v>
       </c>
-      <c r="B234" s="40" t="s">
+      <c r="B234" s="30" t="s">
         <v>466</v>
       </c>
       <c r="C234" s="17" t="s">
@@ -8326,7 +8326,7 @@
         <v>3</v>
       </c>
       <c r="E234" s="16"/>
-      <c r="F234" s="29"/>
+      <c r="F234" s="34"/>
       <c r="G234" s="4"/>
       <c r="H234" s="23"/>
       <c r="I234" t="s">
@@ -8339,7 +8339,7 @@
       <c r="A235" s="16">
         <v>211</v>
       </c>
-      <c r="B235" s="40" t="s">
+      <c r="B235" s="30" t="s">
         <v>98</v>
       </c>
       <c r="C235" s="17" t="s">
@@ -8349,7 +8349,7 @@
         <v>3</v>
       </c>
       <c r="E235" s="16"/>
-      <c r="F235" s="29"/>
+      <c r="F235" s="34"/>
       <c r="G235" s="4"/>
       <c r="H235" s="23"/>
       <c r="I235" t="s">
@@ -8362,7 +8362,7 @@
       <c r="A236" s="16">
         <v>212</v>
       </c>
-      <c r="B236" s="40" t="s">
+      <c r="B236" s="30" t="s">
         <v>101</v>
       </c>
       <c r="C236" s="17" t="s">
@@ -8372,7 +8372,7 @@
         <v>3</v>
       </c>
       <c r="E236" s="16"/>
-      <c r="F236" s="29"/>
+      <c r="F236" s="34"/>
       <c r="G236" s="4"/>
       <c r="H236" s="23"/>
       <c r="I236" t="s">
@@ -8385,7 +8385,7 @@
       <c r="A237" s="16">
         <v>213</v>
       </c>
-      <c r="B237" s="40" t="s">
+      <c r="B237" s="30" t="s">
         <v>127</v>
       </c>
       <c r="C237" s="17" t="s">
@@ -8395,7 +8395,7 @@
         <v>3</v>
       </c>
       <c r="E237" s="16"/>
-      <c r="F237" s="29"/>
+      <c r="F237" s="34"/>
       <c r="G237" s="23" t="s">
         <v>91</v>
       </c>
@@ -8407,34 +8407,34 @@
       <c r="K237" s="4"/>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A238" s="30" t="s">
+      <c r="A238" s="32" t="s">
         <v>494</v>
       </c>
-      <c r="B238" s="30"/>
-      <c r="C238" s="30"/>
-      <c r="D238" s="30"/>
-      <c r="E238" s="30"/>
-      <c r="F238" s="30"/>
-      <c r="G238" s="30"/>
-      <c r="H238" s="30"/>
-      <c r="I238" s="30"/>
-      <c r="J238" s="30"/>
-      <c r="K238" s="30"/>
+      <c r="B238" s="32"/>
+      <c r="C238" s="32"/>
+      <c r="D238" s="32"/>
+      <c r="E238" s="32"/>
+      <c r="F238" s="32"/>
+      <c r="G238" s="32"/>
+      <c r="H238" s="32"/>
+      <c r="I238" s="32"/>
+      <c r="J238" s="32"/>
+      <c r="K238" s="32"/>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A239" s="30" t="s">
+      <c r="A239" s="32" t="s">
         <v>495</v>
       </c>
-      <c r="B239" s="30"/>
-      <c r="C239" s="30"/>
-      <c r="D239" s="30"/>
-      <c r="E239" s="30"/>
-      <c r="F239" s="30"/>
-      <c r="G239" s="30"/>
-      <c r="H239" s="30"/>
-      <c r="I239" s="30"/>
-      <c r="J239" s="30"/>
-      <c r="K239" s="30"/>
+      <c r="B239" s="32"/>
+      <c r="C239" s="32"/>
+      <c r="D239" s="32"/>
+      <c r="E239" s="32"/>
+      <c r="F239" s="32"/>
+      <c r="G239" s="32"/>
+      <c r="H239" s="32"/>
+      <c r="I239" s="32"/>
+      <c r="J239" s="32"/>
+      <c r="K239" s="32"/>
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A240" s="16"/>
@@ -8450,19 +8450,19 @@
       <c r="K240" s="4"/>
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A241" s="31" t="s">
+      <c r="A241" s="33" t="s">
         <v>280</v>
       </c>
-      <c r="B241" s="31"/>
-      <c r="C241" s="31"/>
-      <c r="D241" s="31"/>
-      <c r="E241" s="31"/>
-      <c r="F241" s="31"/>
-      <c r="G241" s="31"/>
-      <c r="H241" s="31"/>
-      <c r="I241" s="31"/>
-      <c r="J241" s="31"/>
-      <c r="K241" s="31"/>
+      <c r="B241" s="33"/>
+      <c r="C241" s="33"/>
+      <c r="D241" s="33"/>
+      <c r="E241" s="33"/>
+      <c r="F241" s="33"/>
+      <c r="G241" s="33"/>
+      <c r="H241" s="33"/>
+      <c r="I241" s="33"/>
+      <c r="J241" s="33"/>
+      <c r="K241" s="33"/>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A242" s="16">
@@ -8603,7 +8603,7 @@
       <c r="A247" s="16">
         <v>219</v>
       </c>
-      <c r="B247" s="40" t="s">
+      <c r="B247" s="30" t="s">
         <v>496</v>
       </c>
       <c r="C247" s="17" t="s">
@@ -8613,7 +8613,7 @@
         <v>2</v>
       </c>
       <c r="E247" s="16"/>
-      <c r="F247" s="29">
+      <c r="F247" s="34">
         <v>6</v>
       </c>
       <c r="G247" s="4"/>
@@ -8628,7 +8628,7 @@
       <c r="A248" s="16">
         <v>220</v>
       </c>
-      <c r="B248" s="40" t="s">
+      <c r="B248" s="30" t="s">
         <v>291</v>
       </c>
       <c r="C248" s="17" t="s">
@@ -8638,7 +8638,7 @@
         <v>2</v>
       </c>
       <c r="E248" s="16"/>
-      <c r="F248" s="29"/>
+      <c r="F248" s="34"/>
       <c r="G248" s="4"/>
       <c r="H248" s="23"/>
       <c r="I248" t="s">
@@ -8651,7 +8651,7 @@
       <c r="A249" s="16">
         <v>221</v>
       </c>
-      <c r="B249" s="40" t="s">
+      <c r="B249" s="30" t="s">
         <v>448</v>
       </c>
       <c r="C249" s="17" t="s">
@@ -8661,7 +8661,7 @@
         <v>3</v>
       </c>
       <c r="E249" s="16"/>
-      <c r="F249" s="29"/>
+      <c r="F249" s="34"/>
       <c r="G249" s="4"/>
       <c r="H249" s="23"/>
       <c r="I249" t="s">
@@ -8674,7 +8674,7 @@
       <c r="A250" s="16">
         <v>222</v>
       </c>
-      <c r="B250" s="40" t="s">
+      <c r="B250" s="30" t="s">
         <v>450</v>
       </c>
       <c r="C250" s="17" t="s">
@@ -8684,7 +8684,7 @@
         <v>3</v>
       </c>
       <c r="E250" s="16"/>
-      <c r="F250" s="29"/>
+      <c r="F250" s="34"/>
       <c r="G250" s="23" t="s">
         <v>9</v>
       </c>
@@ -8699,7 +8699,7 @@
       <c r="A251" s="16">
         <v>223</v>
       </c>
-      <c r="B251" s="40" t="s">
+      <c r="B251" s="30" t="s">
         <v>497</v>
       </c>
       <c r="C251" s="17" t="s">
@@ -8709,7 +8709,7 @@
         <v>2</v>
       </c>
       <c r="E251" s="16"/>
-      <c r="F251" s="29"/>
+      <c r="F251" s="34"/>
       <c r="G251" s="23" t="s">
         <v>92</v>
       </c>
@@ -8724,7 +8724,7 @@
       <c r="A252" s="16">
         <v>224</v>
       </c>
-      <c r="B252" s="40" t="s">
+      <c r="B252" s="30" t="s">
         <v>293</v>
       </c>
       <c r="C252" s="17" t="s">
@@ -8734,7 +8734,7 @@
         <v>2</v>
       </c>
       <c r="E252" s="16"/>
-      <c r="F252" s="29"/>
+      <c r="F252" s="34"/>
       <c r="G252" s="4"/>
       <c r="H252" s="23"/>
       <c r="I252" t="s">
@@ -8747,7 +8747,7 @@
       <c r="A253" s="16">
         <v>225</v>
       </c>
-      <c r="B253" s="40" t="s">
+      <c r="B253" s="30" t="s">
         <v>295</v>
       </c>
       <c r="C253" s="17" t="s">
@@ -8757,7 +8757,7 @@
         <v>3</v>
       </c>
       <c r="E253" s="16"/>
-      <c r="F253" s="29"/>
+      <c r="F253" s="34"/>
       <c r="G253" s="23" t="s">
         <v>92</v>
       </c>
@@ -8878,7 +8878,7 @@
       <c r="A258" s="16">
         <v>230</v>
       </c>
-      <c r="B258" s="40" t="s">
+      <c r="B258" s="30" t="s">
         <v>501</v>
       </c>
       <c r="C258" s="17" t="s">
@@ -8887,10 +8887,10 @@
       <c r="D258" s="16">
         <v>3</v>
       </c>
-      <c r="E258" s="29" t="s">
+      <c r="E258" s="34" t="s">
         <v>356</v>
       </c>
-      <c r="F258" s="29" t="s">
+      <c r="F258" s="34" t="s">
         <v>515</v>
       </c>
       <c r="G258" s="4"/>
@@ -8905,7 +8905,7 @@
       <c r="A259" s="16">
         <v>231</v>
       </c>
-      <c r="B259" s="40" t="s">
+      <c r="B259" s="30" t="s">
         <v>289</v>
       </c>
       <c r="C259" s="17" t="s">
@@ -8914,8 +8914,8 @@
       <c r="D259" s="16">
         <v>3</v>
       </c>
-      <c r="E259" s="29"/>
-      <c r="F259" s="29"/>
+      <c r="E259" s="34"/>
+      <c r="F259" s="34"/>
       <c r="G259" s="23" t="s">
         <v>281</v>
       </c>
@@ -8930,7 +8930,7 @@
       <c r="A260" s="16">
         <v>232</v>
       </c>
-      <c r="B260" s="40" t="s">
+      <c r="B260" s="30" t="s">
         <v>300</v>
       </c>
       <c r="C260" s="17" t="s">
@@ -8939,8 +8939,8 @@
       <c r="D260" s="16">
         <v>3</v>
       </c>
-      <c r="E260" s="29"/>
-      <c r="F260" s="29"/>
+      <c r="E260" s="34"/>
+      <c r="F260" s="34"/>
       <c r="G260" s="23" t="s">
         <v>282</v>
       </c>
@@ -8955,7 +8955,7 @@
       <c r="A261" s="16">
         <v>233</v>
       </c>
-      <c r="B261" s="40" t="s">
+      <c r="B261" s="30" t="s">
         <v>368</v>
       </c>
       <c r="C261" s="17" t="s">
@@ -8964,8 +8964,8 @@
       <c r="D261" s="16">
         <v>3</v>
       </c>
-      <c r="E261" s="29"/>
-      <c r="F261" s="29"/>
+      <c r="E261" s="34"/>
+      <c r="F261" s="34"/>
       <c r="G261" s="4"/>
       <c r="H261" s="23"/>
       <c r="I261" t="s">
@@ -8978,7 +8978,7 @@
       <c r="A262" s="16">
         <v>234</v>
       </c>
-      <c r="B262" s="40" t="s">
+      <c r="B262" s="30" t="s">
         <v>292</v>
       </c>
       <c r="C262" s="17" t="s">
@@ -8987,8 +8987,8 @@
       <c r="D262" s="16">
         <v>2</v>
       </c>
-      <c r="E262" s="29"/>
-      <c r="F262" s="29"/>
+      <c r="E262" s="34"/>
+      <c r="F262" s="34"/>
       <c r="G262" s="23" t="s">
         <v>281</v>
       </c>
@@ -9003,7 +9003,7 @@
       <c r="A263" s="16">
         <v>235</v>
       </c>
-      <c r="B263" s="40" t="s">
+      <c r="B263" s="30" t="s">
         <v>307</v>
       </c>
       <c r="C263" s="17" t="s">
@@ -9012,8 +9012,8 @@
       <c r="D263" s="16">
         <v>3</v>
       </c>
-      <c r="E263" s="29"/>
-      <c r="F263" s="29"/>
+      <c r="E263" s="34"/>
+      <c r="F263" s="34"/>
       <c r="G263" s="23" t="s">
         <v>91</v>
       </c>
@@ -9028,7 +9028,7 @@
       <c r="A264" s="16">
         <v>236</v>
       </c>
-      <c r="B264" s="40" t="s">
+      <c r="B264" s="30" t="s">
         <v>126</v>
       </c>
       <c r="C264" s="17" t="s">
@@ -9037,10 +9037,10 @@
       <c r="D264" s="16">
         <v>3</v>
       </c>
-      <c r="E264" s="29" t="s">
+      <c r="E264" s="34" t="s">
         <v>357</v>
       </c>
-      <c r="F264" s="29"/>
+      <c r="F264" s="34"/>
       <c r="G264" s="4"/>
       <c r="H264" s="23"/>
       <c r="I264" t="s">
@@ -9053,7 +9053,7 @@
       <c r="A265" s="16">
         <v>237</v>
       </c>
-      <c r="B265" s="40" t="s">
+      <c r="B265" s="30" t="s">
         <v>312</v>
       </c>
       <c r="C265" s="17" t="s">
@@ -9062,8 +9062,8 @@
       <c r="D265" s="16">
         <v>3</v>
       </c>
-      <c r="E265" s="29"/>
-      <c r="F265" s="29"/>
+      <c r="E265" s="34"/>
+      <c r="F265" s="34"/>
       <c r="G265" s="23" t="s">
         <v>282</v>
       </c>
@@ -9078,7 +9078,7 @@
       <c r="A266" s="16">
         <v>238</v>
       </c>
-      <c r="B266" s="40" t="s">
+      <c r="B266" s="30" t="s">
         <v>502</v>
       </c>
       <c r="C266" s="17" t="s">
@@ -9087,8 +9087,8 @@
       <c r="D266" s="16">
         <v>3</v>
       </c>
-      <c r="E266" s="29"/>
-      <c r="F266" s="29"/>
+      <c r="E266" s="34"/>
+      <c r="F266" s="34"/>
       <c r="G266" s="4"/>
       <c r="H266" s="23"/>
       <c r="I266" t="s">
@@ -9101,7 +9101,7 @@
       <c r="A267" s="16">
         <v>239</v>
       </c>
-      <c r="B267" s="40" t="s">
+      <c r="B267" s="30" t="s">
         <v>297</v>
       </c>
       <c r="C267" s="17" t="s">
@@ -9110,8 +9110,8 @@
       <c r="D267" s="16">
         <v>3</v>
       </c>
-      <c r="E267" s="29"/>
-      <c r="F267" s="29"/>
+      <c r="E267" s="34"/>
+      <c r="F267" s="34"/>
       <c r="G267" s="4"/>
       <c r="H267" s="23"/>
       <c r="I267" t="s">
@@ -9124,7 +9124,7 @@
       <c r="A268" s="16">
         <v>240</v>
       </c>
-      <c r="B268" s="40" t="s">
+      <c r="B268" s="30" t="s">
         <v>314</v>
       </c>
       <c r="C268" s="17" t="s">
@@ -9133,8 +9133,8 @@
       <c r="D268" s="16">
         <v>3</v>
       </c>
-      <c r="E268" s="29"/>
-      <c r="F268" s="29"/>
+      <c r="E268" s="34"/>
+      <c r="F268" s="34"/>
       <c r="G268" s="23" t="s">
         <v>92</v>
       </c>
@@ -9149,7 +9149,7 @@
       <c r="A269" s="16">
         <v>241</v>
       </c>
-      <c r="B269" s="40" t="s">
+      <c r="B269" s="30" t="s">
         <v>503</v>
       </c>
       <c r="C269" s="17" t="s">
@@ -9159,7 +9159,7 @@
         <v>15</v>
       </c>
       <c r="E269" s="16"/>
-      <c r="F269" s="29">
+      <c r="F269" s="34">
         <v>15</v>
       </c>
       <c r="G269" s="4" t="s">
@@ -9176,7 +9176,7 @@
       <c r="A270" s="16">
         <v>242</v>
       </c>
-      <c r="B270" s="40" t="s">
+      <c r="B270" s="30" t="s">
         <v>504</v>
       </c>
       <c r="C270" s="17" t="s">
@@ -9186,7 +9186,7 @@
         <v>6</v>
       </c>
       <c r="E270" s="16"/>
-      <c r="F270" s="29"/>
+      <c r="F270" s="34"/>
       <c r="G270" s="4" t="s">
         <v>208</v>
       </c>
@@ -9201,7 +9201,7 @@
       <c r="A271" s="16">
         <v>243</v>
       </c>
-      <c r="B271" s="40" t="s">
+      <c r="B271" s="30" t="s">
         <v>306</v>
       </c>
       <c r="C271" s="17" t="s">
@@ -9211,7 +9211,7 @@
         <v>2</v>
       </c>
       <c r="E271" s="16"/>
-      <c r="F271" s="29"/>
+      <c r="F271" s="34"/>
       <c r="G271" s="23" t="s">
         <v>91</v>
       </c>
@@ -9226,7 +9226,7 @@
       <c r="A272" s="16">
         <v>244</v>
       </c>
-      <c r="B272" s="40" t="s">
+      <c r="B272" s="30" t="s">
         <v>110</v>
       </c>
       <c r="C272" s="17" t="s">
@@ -9236,7 +9236,7 @@
         <v>3</v>
       </c>
       <c r="E272" s="16"/>
-      <c r="F272" s="29"/>
+      <c r="F272" s="34"/>
       <c r="G272" s="4"/>
       <c r="H272" s="23"/>
       <c r="I272" t="s">
@@ -9249,7 +9249,7 @@
       <c r="A273" s="16">
         <v>245</v>
       </c>
-      <c r="B273" s="40" t="s">
+      <c r="B273" s="30" t="s">
         <v>308</v>
       </c>
       <c r="C273" s="17" t="s">
@@ -9259,7 +9259,7 @@
         <v>3</v>
       </c>
       <c r="E273" s="16"/>
-      <c r="F273" s="29"/>
+      <c r="F273" s="34"/>
       <c r="G273" s="23" t="s">
         <v>91</v>
       </c>
@@ -9274,7 +9274,7 @@
       <c r="A274" s="16">
         <v>246</v>
       </c>
-      <c r="B274" s="40" t="s">
+      <c r="B274" s="30" t="s">
         <v>129</v>
       </c>
       <c r="C274" s="17" t="s">
@@ -9284,7 +9284,7 @@
         <v>3</v>
       </c>
       <c r="E274" s="16"/>
-      <c r="F274" s="29"/>
+      <c r="F274" s="34"/>
       <c r="G274" s="23" t="s">
         <v>13</v>
       </c>
@@ -9299,7 +9299,7 @@
       <c r="A275" s="16">
         <v>247</v>
       </c>
-      <c r="B275" s="40" t="s">
+      <c r="B275" s="30" t="s">
         <v>287</v>
       </c>
       <c r="C275" s="17" t="s">
@@ -9309,7 +9309,7 @@
         <v>3</v>
       </c>
       <c r="E275" s="16"/>
-      <c r="F275" s="29"/>
+      <c r="F275" s="34"/>
       <c r="G275" s="4"/>
       <c r="H275" s="23"/>
       <c r="I275" t="s">
@@ -9322,7 +9322,7 @@
       <c r="A276" s="16">
         <v>248</v>
       </c>
-      <c r="B276" s="40" t="s">
+      <c r="B276" s="30" t="s">
         <v>310</v>
       </c>
       <c r="C276" s="17" t="s">
@@ -9332,7 +9332,7 @@
         <v>3</v>
       </c>
       <c r="E276" s="16"/>
-      <c r="F276" s="29"/>
+      <c r="F276" s="34"/>
       <c r="G276" s="23" t="s">
         <v>363</v>
       </c>
@@ -9347,7 +9347,7 @@
       <c r="A277" s="16">
         <v>249</v>
       </c>
-      <c r="B277" s="40" t="s">
+      <c r="B277" s="30" t="s">
         <v>311</v>
       </c>
       <c r="C277" s="17" t="s">
@@ -9357,7 +9357,7 @@
         <v>3</v>
       </c>
       <c r="E277" s="16"/>
-      <c r="F277" s="29"/>
+      <c r="F277" s="34"/>
       <c r="G277" s="23" t="s">
         <v>363</v>
       </c>
@@ -9372,7 +9372,7 @@
       <c r="A278" s="16">
         <v>250</v>
       </c>
-      <c r="B278" s="40" t="s">
+      <c r="B278" s="30" t="s">
         <v>313</v>
       </c>
       <c r="C278" s="17" t="s">
@@ -9382,7 +9382,7 @@
         <v>3</v>
       </c>
       <c r="E278" s="16"/>
-      <c r="F278" s="29"/>
+      <c r="F278" s="34"/>
       <c r="G278" s="4"/>
       <c r="H278" s="23"/>
       <c r="I278" t="s">
@@ -9395,7 +9395,7 @@
       <c r="A279" s="16">
         <v>251</v>
       </c>
-      <c r="B279" s="40" t="s">
+      <c r="B279" s="30" t="s">
         <v>315</v>
       </c>
       <c r="C279" s="17" t="s">
@@ -9405,7 +9405,7 @@
         <v>3</v>
       </c>
       <c r="E279" s="16"/>
-      <c r="F279" s="29"/>
+      <c r="F279" s="34"/>
       <c r="G279" s="4"/>
       <c r="H279" s="23"/>
       <c r="I279" t="s">
@@ -9418,7 +9418,7 @@
       <c r="A280" s="16">
         <v>252</v>
       </c>
-      <c r="B280" s="40" t="s">
+      <c r="B280" s="30" t="s">
         <v>283</v>
       </c>
       <c r="C280" s="17" t="s">
@@ -9428,7 +9428,7 @@
         <v>3</v>
       </c>
       <c r="E280" s="16"/>
-      <c r="F280" s="29"/>
+      <c r="F280" s="34"/>
       <c r="G280" s="4"/>
       <c r="H280" s="23"/>
       <c r="I280" t="s">
@@ -9441,7 +9441,7 @@
       <c r="A281" s="16">
         <v>253</v>
       </c>
-      <c r="B281" s="40" t="s">
+      <c r="B281" s="30" t="s">
         <v>316</v>
       </c>
       <c r="C281" s="17" t="s">
@@ -9451,7 +9451,7 @@
         <v>3</v>
       </c>
       <c r="E281" s="16"/>
-      <c r="F281" s="29"/>
+      <c r="F281" s="34"/>
       <c r="G281" s="4"/>
       <c r="H281" s="23"/>
       <c r="I281" t="s">
@@ -9461,34 +9461,34 @@
       <c r="K281" s="4"/>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A282" s="30" t="s">
+      <c r="A282" s="32" t="s">
         <v>494</v>
       </c>
-      <c r="B282" s="30"/>
-      <c r="C282" s="30"/>
-      <c r="D282" s="30"/>
-      <c r="E282" s="30"/>
-      <c r="F282" s="30"/>
-      <c r="G282" s="30"/>
-      <c r="H282" s="30"/>
-      <c r="I282" s="30"/>
-      <c r="J282" s="30"/>
-      <c r="K282" s="30"/>
+      <c r="B282" s="32"/>
+      <c r="C282" s="32"/>
+      <c r="D282" s="32"/>
+      <c r="E282" s="32"/>
+      <c r="F282" s="32"/>
+      <c r="G282" s="32"/>
+      <c r="H282" s="32"/>
+      <c r="I282" s="32"/>
+      <c r="J282" s="32"/>
+      <c r="K282" s="32"/>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A283" s="30" t="s">
+      <c r="A283" s="32" t="s">
         <v>495</v>
       </c>
-      <c r="B283" s="30"/>
-      <c r="C283" s="30"/>
-      <c r="D283" s="30"/>
-      <c r="E283" s="30"/>
-      <c r="F283" s="30"/>
-      <c r="G283" s="30"/>
-      <c r="H283" s="30"/>
-      <c r="I283" s="30"/>
-      <c r="J283" s="30"/>
-      <c r="K283" s="30"/>
+      <c r="B283" s="32"/>
+      <c r="C283" s="32"/>
+      <c r="D283" s="32"/>
+      <c r="E283" s="32"/>
+      <c r="F283" s="32"/>
+      <c r="G283" s="32"/>
+      <c r="H283" s="32"/>
+      <c r="I283" s="32"/>
+      <c r="J283" s="32"/>
+      <c r="K283" s="32"/>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A284" s="26"/>
@@ -9946,30 +9946,30 @@
       <c r="K318" s="28"/>
     </row>
     <row r="319" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A319" s="32"/>
-      <c r="B319" s="32"/>
-      <c r="C319" s="32"/>
-      <c r="D319" s="32"/>
-      <c r="E319" s="32"/>
-      <c r="F319" s="32"/>
-      <c r="G319" s="32"/>
-      <c r="H319" s="32"/>
-      <c r="I319" s="32"/>
-      <c r="J319" s="32"/>
-      <c r="K319" s="32"/>
+      <c r="A319" s="38"/>
+      <c r="B319" s="38"/>
+      <c r="C319" s="38"/>
+      <c r="D319" s="38"/>
+      <c r="E319" s="38"/>
+      <c r="F319" s="38"/>
+      <c r="G319" s="38"/>
+      <c r="H319" s="38"/>
+      <c r="I319" s="38"/>
+      <c r="J319" s="38"/>
+      <c r="K319" s="38"/>
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A320" s="32"/>
-      <c r="B320" s="32"/>
-      <c r="C320" s="32"/>
-      <c r="D320" s="32"/>
-      <c r="E320" s="32"/>
-      <c r="F320" s="32"/>
-      <c r="G320" s="32"/>
-      <c r="H320" s="32"/>
-      <c r="I320" s="32"/>
-      <c r="J320" s="32"/>
-      <c r="K320" s="32"/>
+      <c r="A320" s="38"/>
+      <c r="B320" s="38"/>
+      <c r="C320" s="38"/>
+      <c r="D320" s="38"/>
+      <c r="E320" s="38"/>
+      <c r="F320" s="38"/>
+      <c r="G320" s="38"/>
+      <c r="H320" s="38"/>
+      <c r="I320" s="38"/>
+      <c r="J320" s="38"/>
+      <c r="K320" s="38"/>
     </row>
     <row r="321" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A321" s="26"/>
@@ -12742,35 +12742,14 @@
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A91:K91"/>
-    <mergeCell ref="A92:K92"/>
-    <mergeCell ref="A57:K57"/>
-    <mergeCell ref="A59:K59"/>
-    <mergeCell ref="A39:K39"/>
-    <mergeCell ref="E8:E13"/>
-    <mergeCell ref="E14:E19"/>
-    <mergeCell ref="F8:F19"/>
-    <mergeCell ref="F79:F90"/>
-    <mergeCell ref="F26:F32"/>
-    <mergeCell ref="F60:F62"/>
-    <mergeCell ref="F74:F77"/>
-    <mergeCell ref="A41:K41"/>
-    <mergeCell ref="A94:K94"/>
-    <mergeCell ref="A134:K134"/>
-    <mergeCell ref="A135:K135"/>
-    <mergeCell ref="A137:K137"/>
-    <mergeCell ref="A165:K165"/>
-    <mergeCell ref="A166:K166"/>
-    <mergeCell ref="A168:K168"/>
-    <mergeCell ref="A196:K196"/>
-    <mergeCell ref="A197:K197"/>
-    <mergeCell ref="A199:K199"/>
-    <mergeCell ref="A283:K283"/>
-    <mergeCell ref="E258:E263"/>
-    <mergeCell ref="E264:E268"/>
-    <mergeCell ref="F258:F268"/>
-    <mergeCell ref="F269:F281"/>
+    <mergeCell ref="E215:E218"/>
+    <mergeCell ref="E219:E223"/>
+    <mergeCell ref="F215:F223"/>
+    <mergeCell ref="F225:F237"/>
+    <mergeCell ref="F247:F253"/>
+    <mergeCell ref="A238:K238"/>
+    <mergeCell ref="A239:K239"/>
+    <mergeCell ref="A241:K241"/>
     <mergeCell ref="A319:K319"/>
     <mergeCell ref="A320:K320"/>
     <mergeCell ref="E101:E106"/>
@@ -12787,14 +12766,35 @@
     <mergeCell ref="F201:F203"/>
     <mergeCell ref="F210:F213"/>
     <mergeCell ref="A282:K282"/>
-    <mergeCell ref="E215:E218"/>
-    <mergeCell ref="E219:E223"/>
-    <mergeCell ref="F215:F223"/>
-    <mergeCell ref="F225:F237"/>
-    <mergeCell ref="F247:F253"/>
-    <mergeCell ref="A238:K238"/>
-    <mergeCell ref="A239:K239"/>
-    <mergeCell ref="A241:K241"/>
+    <mergeCell ref="A283:K283"/>
+    <mergeCell ref="E258:E263"/>
+    <mergeCell ref="E264:E268"/>
+    <mergeCell ref="F258:F268"/>
+    <mergeCell ref="F269:F281"/>
+    <mergeCell ref="A166:K166"/>
+    <mergeCell ref="A168:K168"/>
+    <mergeCell ref="A196:K196"/>
+    <mergeCell ref="A197:K197"/>
+    <mergeCell ref="A199:K199"/>
+    <mergeCell ref="A94:K94"/>
+    <mergeCell ref="A134:K134"/>
+    <mergeCell ref="A135:K135"/>
+    <mergeCell ref="A137:K137"/>
+    <mergeCell ref="A165:K165"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A91:K91"/>
+    <mergeCell ref="A92:K92"/>
+    <mergeCell ref="A57:K57"/>
+    <mergeCell ref="A59:K59"/>
+    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="E8:E13"/>
+    <mergeCell ref="E14:E19"/>
+    <mergeCell ref="F8:F19"/>
+    <mergeCell ref="F79:F90"/>
+    <mergeCell ref="F26:F32"/>
+    <mergeCell ref="F60:F62"/>
+    <mergeCell ref="F74:F77"/>
+    <mergeCell ref="A41:K41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12811,10 +12811,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="40" t="s">
         <v>209</v>
       </c>
-      <c r="B1" s="38"/>
+      <c r="B1" s="40"/>
     </row>
     <row r="2" spans="1:2" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -12825,7 +12825,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="37">
+      <c r="A3" s="39">
         <v>1</v>
       </c>
       <c r="B3" s="19" t="s">
@@ -12833,37 +12833,37 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="37"/>
+      <c r="A4" s="39"/>
       <c r="B4" s="19" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="37"/>
+      <c r="A5" s="39"/>
       <c r="B5" s="19" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="37"/>
+      <c r="A6" s="39"/>
       <c r="B6" s="19" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="37"/>
+      <c r="A7" s="39"/>
       <c r="B7" s="19" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="37"/>
+      <c r="A8" s="39"/>
       <c r="B8" s="19" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="37">
+      <c r="A9" s="39">
         <v>2</v>
       </c>
       <c r="B9" s="19" t="s">
@@ -12871,31 +12871,31 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="37"/>
+      <c r="A10" s="39"/>
       <c r="B10" s="19" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="37"/>
+      <c r="A11" s="39"/>
       <c r="B11" s="19" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="37"/>
+      <c r="A12" s="39"/>
       <c r="B12" s="19" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="37"/>
+      <c r="A13" s="39"/>
       <c r="B13" s="19" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="37">
+      <c r="A14" s="39">
         <v>3</v>
       </c>
       <c r="B14" s="19" t="s">
@@ -12903,37 +12903,37 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="37"/>
+      <c r="A15" s="39"/>
       <c r="B15" s="19" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="37"/>
+      <c r="A16" s="39"/>
       <c r="B16" s="19" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
+      <c r="A17" s="39"/>
       <c r="B17" s="19" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="37"/>
+      <c r="A18" s="39"/>
       <c r="B18" s="19" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="37"/>
+      <c r="A19" s="39"/>
       <c r="B19" s="19" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="37">
+      <c r="A20" s="39">
         <v>4</v>
       </c>
       <c r="B20" s="19" t="s">
@@ -12941,37 +12941,37 @@
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="37"/>
+      <c r="A21" s="39"/>
       <c r="B21" s="19" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="37"/>
+      <c r="A22" s="39"/>
       <c r="B22" s="19" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="37"/>
+      <c r="A23" s="39"/>
       <c r="B23" s="19" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="37"/>
+      <c r="A24" s="39"/>
       <c r="B24" s="19" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="37"/>
+      <c r="A25" s="39"/>
       <c r="B25" s="19" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="37">
+      <c r="A26" s="39">
         <v>5</v>
       </c>
       <c r="B26" s="19" t="s">
@@ -12979,73 +12979,73 @@
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="37"/>
+      <c r="A27" s="39"/>
       <c r="B27" s="19" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="37"/>
+      <c r="A28" s="39"/>
       <c r="B28" s="19" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="37"/>
+      <c r="A29" s="39"/>
       <c r="B29" s="19" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="37"/>
+      <c r="A30" s="39"/>
       <c r="B30" s="19" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="37"/>
+      <c r="A31" s="39"/>
       <c r="B31" s="19" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="37"/>
+      <c r="A32" s="39"/>
       <c r="B32" s="19" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="37"/>
+      <c r="A33" s="39"/>
       <c r="B33" s="19" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="37"/>
+      <c r="A34" s="39"/>
       <c r="B34" s="19" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="37"/>
+      <c r="A35" s="39"/>
       <c r="B35" s="19" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="37"/>
+      <c r="A36" s="39"/>
       <c r="B36" s="19" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="37"/>
+      <c r="A37" s="39"/>
       <c r="B37" s="19" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="37">
+      <c r="A38" s="39">
         <v>6</v>
       </c>
       <c r="B38" s="19" t="s">
@@ -13053,25 +13053,25 @@
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="37"/>
+      <c r="A39" s="39"/>
       <c r="B39" s="19" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="37"/>
+      <c r="A40" s="39"/>
       <c r="B40" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="37"/>
+      <c r="A41" s="39"/>
       <c r="B41" s="19" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="37"/>
+      <c r="A42" s="39"/>
       <c r="B42" s="19" t="s">
         <v>72</v>
       </c>
@@ -13103,7 +13103,7 @@
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="37">
+      <c r="A47" s="39">
         <v>8</v>
       </c>
       <c r="B47" s="19" t="s">
@@ -13111,25 +13111,25 @@
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="37"/>
+      <c r="A48" s="39"/>
       <c r="B48" s="19" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="37"/>
+      <c r="A49" s="39"/>
       <c r="B49" s="19" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="37"/>
+      <c r="A50" s="39"/>
       <c r="B50" s="19" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="37">
+      <c r="A51" s="39">
         <v>9</v>
       </c>
       <c r="B51" s="19" t="s">
@@ -13137,25 +13137,25 @@
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="37"/>
+      <c r="A52" s="39"/>
       <c r="B52" s="19" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="37"/>
+      <c r="A53" s="39"/>
       <c r="B53" s="19" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="37"/>
+      <c r="A54" s="39"/>
       <c r="B54" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="37">
+      <c r="A55" s="39">
         <v>10</v>
       </c>
       <c r="B55" s="19" t="s">
@@ -13163,43 +13163,43 @@
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="37"/>
+      <c r="A56" s="39"/>
       <c r="B56" s="19" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="37"/>
+      <c r="A57" s="39"/>
       <c r="B57" s="19" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="37"/>
+      <c r="A58" s="39"/>
       <c r="B58" s="19" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="37"/>
+      <c r="A59" s="39"/>
       <c r="B59" s="19" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="37"/>
+      <c r="A60" s="39"/>
       <c r="B60" s="19" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="37"/>
+      <c r="A61" s="39"/>
       <c r="B61" s="19" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="37">
+      <c r="A62" s="39">
         <v>11</v>
       </c>
       <c r="B62" s="19" t="s">
@@ -13207,37 +13207,37 @@
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="37"/>
+      <c r="A63" s="39"/>
       <c r="B63" s="19" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="37"/>
+      <c r="A64" s="39"/>
       <c r="B64" s="19" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="37"/>
+      <c r="A65" s="39"/>
       <c r="B65" s="19" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="37"/>
+      <c r="A66" s="39"/>
       <c r="B66" s="19" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="37"/>
+      <c r="A67" s="39"/>
       <c r="B67" s="19" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="37">
+      <c r="A68" s="39">
         <v>12</v>
       </c>
       <c r="B68" s="19" t="s">
@@ -13245,67 +13245,67 @@
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="37"/>
+      <c r="A69" s="39"/>
       <c r="B69" s="19" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="37"/>
+      <c r="A70" s="39"/>
       <c r="B70" s="19" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="37"/>
+      <c r="A71" s="39"/>
       <c r="B71" s="19" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="37"/>
+      <c r="A72" s="39"/>
       <c r="B72" s="19" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="37"/>
+      <c r="A73" s="39"/>
       <c r="B73" s="19" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="37"/>
+      <c r="A74" s="39"/>
       <c r="B74" s="19" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="37"/>
+      <c r="A75" s="39"/>
       <c r="B75" s="19" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="37"/>
+      <c r="A76" s="39"/>
       <c r="B76" s="19" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="37"/>
+      <c r="A77" s="39"/>
       <c r="B77" s="19" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="37"/>
+      <c r="A78" s="39"/>
       <c r="B78" s="19" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="37"/>
+      <c r="A79" s="39"/>
       <c r="B79" s="19" t="s">
         <v>120</v>
       </c>
@@ -13395,10 +13395,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="40" t="s">
         <v>663</v>
       </c>
-      <c r="B1" s="38"/>
+      <c r="B1" s="40"/>
     </row>
     <row r="2" spans="1:2" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -13409,7 +13409,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="37">
+      <c r="A3" s="39">
         <v>1</v>
       </c>
       <c r="B3" s="17" t="s">
@@ -13417,37 +13417,37 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="37"/>
+      <c r="A4" s="39"/>
       <c r="B4" s="17" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="37"/>
+      <c r="A5" s="39"/>
       <c r="B5" s="17" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="37"/>
+      <c r="A6" s="39"/>
       <c r="B6" s="17" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="37"/>
+      <c r="A7" s="39"/>
       <c r="B7" s="17" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="37"/>
+      <c r="A8" s="39"/>
       <c r="B8" s="17" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="37">
+      <c r="A9" s="39">
         <v>2</v>
       </c>
       <c r="B9" s="17" t="s">
@@ -13455,31 +13455,31 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="37"/>
+      <c r="A10" s="39"/>
       <c r="B10" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="37"/>
+      <c r="A11" s="39"/>
       <c r="B11" s="17" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="37"/>
+      <c r="A12" s="39"/>
       <c r="B12" s="17" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="37"/>
+      <c r="A13" s="39"/>
       <c r="B13" s="17" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="37">
+      <c r="A14" s="39">
         <v>3</v>
       </c>
       <c r="B14" s="17" t="s">
@@ -13487,37 +13487,37 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="37"/>
+      <c r="A15" s="39"/>
       <c r="B15" s="17" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="37"/>
+      <c r="A16" s="39"/>
       <c r="B16" s="17" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
+      <c r="A17" s="39"/>
       <c r="B17" s="17" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="37"/>
+      <c r="A18" s="39"/>
       <c r="B18" s="17" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="37"/>
+      <c r="A19" s="39"/>
       <c r="B19" s="17" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="37">
+      <c r="A20" s="39">
         <v>4</v>
       </c>
       <c r="B20" s="17" t="s">
@@ -13525,37 +13525,37 @@
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="37"/>
+      <c r="A21" s="39"/>
       <c r="B21" s="17" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="37"/>
+      <c r="A22" s="39"/>
       <c r="B22" s="17" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="37"/>
+      <c r="A23" s="39"/>
       <c r="B23" s="17" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="37"/>
+      <c r="A24" s="39"/>
       <c r="B24" s="17" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="37"/>
+      <c r="A25" s="39"/>
       <c r="B25" s="17" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="37">
+      <c r="A26" s="39">
         <v>5</v>
       </c>
       <c r="B26" s="17" t="s">
@@ -13563,25 +13563,25 @@
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="37"/>
+      <c r="A27" s="39"/>
       <c r="B27" s="17" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="37"/>
+      <c r="A28" s="39"/>
       <c r="B28" s="17" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="37"/>
+      <c r="A29" s="39"/>
       <c r="B29" s="17" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="37">
+      <c r="A30" s="39">
         <v>6</v>
       </c>
       <c r="B30" s="17" t="s">
@@ -13589,31 +13589,31 @@
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="37"/>
+      <c r="A31" s="39"/>
       <c r="B31" s="17" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="37"/>
+      <c r="A32" s="39"/>
       <c r="B32" s="17" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="37"/>
+      <c r="A33" s="39"/>
       <c r="B33" s="17" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="37"/>
+      <c r="A34" s="39"/>
       <c r="B34" s="17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="37">
+      <c r="A35" s="39">
         <v>7</v>
       </c>
       <c r="B35" s="17" t="s">
@@ -13621,31 +13621,31 @@
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="37"/>
+      <c r="A36" s="39"/>
       <c r="B36" s="17" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="37"/>
+      <c r="A37" s="39"/>
       <c r="B37" s="17" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="37"/>
+      <c r="A38" s="39"/>
       <c r="B38" s="17" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="37"/>
+      <c r="A39" s="39"/>
       <c r="B39" s="17" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="37">
+      <c r="A40" s="39">
         <v>8</v>
       </c>
       <c r="B40" s="17" t="s">
@@ -13653,25 +13653,25 @@
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="37"/>
+      <c r="A41" s="39"/>
       <c r="B41" s="17" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="37"/>
+      <c r="A42" s="39"/>
       <c r="B42" s="17" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="37"/>
+      <c r="A43" s="39"/>
       <c r="B43" s="17" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="37">
+      <c r="A44" s="39">
         <v>9</v>
       </c>
       <c r="B44" s="17" t="s">
@@ -13679,67 +13679,67 @@
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="37"/>
+      <c r="A45" s="39"/>
       <c r="B45" s="17" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="37"/>
+      <c r="A46" s="39"/>
       <c r="B46" s="17" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="37"/>
+      <c r="A47" s="39"/>
       <c r="B47" s="17" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="37"/>
+      <c r="A48" s="39"/>
       <c r="B48" s="17" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="37"/>
+      <c r="A49" s="39"/>
       <c r="B49" s="17" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="37"/>
+      <c r="A50" s="39"/>
       <c r="B50" s="17" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="37"/>
+      <c r="A51" s="39"/>
       <c r="B51" s="17" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="37"/>
+      <c r="A52" s="39"/>
       <c r="B52" s="17" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="37"/>
+      <c r="A53" s="39"/>
       <c r="B53" s="17" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="37"/>
+      <c r="A54" s="39"/>
       <c r="B54" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="37">
+      <c r="A55" s="39">
         <v>10</v>
       </c>
       <c r="B55" s="17" t="s">
@@ -13747,79 +13747,79 @@
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="37"/>
+      <c r="A56" s="39"/>
       <c r="B56" s="17" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="37"/>
+      <c r="A57" s="39"/>
       <c r="B57" s="17" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="37"/>
+      <c r="A58" s="39"/>
       <c r="B58" s="17" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="37"/>
+      <c r="A59" s="39"/>
       <c r="B59" s="17" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="37"/>
+      <c r="A60" s="39"/>
       <c r="B60" s="17" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="37"/>
+      <c r="A61" s="39"/>
       <c r="B61" s="17" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="37"/>
+      <c r="A62" s="39"/>
       <c r="B62" s="17" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="37"/>
+      <c r="A63" s="39"/>
       <c r="B63" s="17" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="37"/>
+      <c r="A64" s="39"/>
       <c r="B64" s="17" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="37"/>
+      <c r="A65" s="39"/>
       <c r="B65" s="17" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="37"/>
+      <c r="A66" s="39"/>
       <c r="B66" s="17" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="37"/>
+      <c r="A67" s="39"/>
       <c r="B67" s="17" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="37">
+      <c r="A68" s="39">
         <v>11</v>
       </c>
       <c r="B68" s="17" t="s">
@@ -13827,25 +13827,25 @@
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="37"/>
+      <c r="A69" s="39"/>
       <c r="B69" s="17" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="37"/>
+      <c r="A70" s="39"/>
       <c r="B70" s="17" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="37"/>
+      <c r="A71" s="39"/>
       <c r="B71" s="17" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="37">
+      <c r="A72" s="39">
         <v>12</v>
       </c>
       <c r="B72" s="17" t="s">
@@ -13853,91 +13853,91 @@
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="37"/>
+      <c r="A73" s="39"/>
       <c r="B73" s="17" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="37"/>
+      <c r="A74" s="39"/>
       <c r="B74" s="17" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="37"/>
+      <c r="A75" s="39"/>
       <c r="B75" s="17" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="37"/>
+      <c r="A76" s="39"/>
       <c r="B76" s="17" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="37"/>
+      <c r="A77" s="39"/>
       <c r="B77" s="17" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="37"/>
+      <c r="A78" s="39"/>
       <c r="B78" s="17" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="37"/>
+      <c r="A79" s="39"/>
       <c r="B79" s="17" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="37"/>
+      <c r="A80" s="39"/>
       <c r="B80" s="17" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" s="37"/>
+      <c r="A81" s="39"/>
       <c r="B81" s="17" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" s="37"/>
+      <c r="A82" s="39"/>
       <c r="B82" s="17" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" s="37"/>
+      <c r="A83" s="39"/>
       <c r="B83" s="17" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84" s="37"/>
+      <c r="A84" s="39"/>
       <c r="B84" s="17" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85" s="37"/>
+      <c r="A85" s="39"/>
       <c r="B85" s="17" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86" s="37"/>
+      <c r="A86" s="39"/>
       <c r="B86" s="17" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A87" s="37"/>
+      <c r="A87" s="39"/>
       <c r="B87" s="17" t="s">
         <v>316</v>
       </c>
@@ -13981,10 +13981,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="40" t="s">
         <v>665</v>
       </c>
-      <c r="B1" s="38"/>
+      <c r="B1" s="40"/>
     </row>
     <row r="2" spans="1:2" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -13995,7 +13995,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="37">
+      <c r="A3" s="39">
         <v>1</v>
       </c>
       <c r="B3" s="17" t="s">
@@ -14003,37 +14003,37 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="37"/>
+      <c r="A4" s="39"/>
       <c r="B4" s="17" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="37"/>
+      <c r="A5" s="39"/>
       <c r="B5" s="17" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="37"/>
+      <c r="A6" s="39"/>
       <c r="B6" s="17" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="37"/>
+      <c r="A7" s="39"/>
       <c r="B7" s="17" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="37"/>
+      <c r="A8" s="39"/>
       <c r="B8" s="17" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="37">
+      <c r="A9" s="39">
         <v>2</v>
       </c>
       <c r="B9" s="17" t="s">
@@ -14041,61 +14041,61 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="37"/>
+      <c r="A10" s="39"/>
       <c r="B10" s="17" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="37"/>
+      <c r="A11" s="39"/>
       <c r="B11" s="17" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="37"/>
+      <c r="A12" s="39"/>
       <c r="B12" s="17" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="37"/>
+      <c r="A13" s="39"/>
       <c r="B13" s="17" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="37"/>
+      <c r="A14" s="39"/>
       <c r="B14" s="17" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="37"/>
+      <c r="A15" s="39"/>
       <c r="B15" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="37"/>
+      <c r="A16" s="39"/>
       <c r="B16" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
+      <c r="A17" s="39"/>
       <c r="B17" s="17" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="37"/>
+      <c r="A18" s="39"/>
       <c r="B18" s="17" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="37">
+      <c r="A19" s="39">
         <v>3</v>
       </c>
       <c r="B19" s="17" t="s">
@@ -14103,37 +14103,37 @@
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="37"/>
+      <c r="A20" s="39"/>
       <c r="B20" s="17" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="37"/>
+      <c r="A21" s="39"/>
       <c r="B21" s="17" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="37"/>
+      <c r="A22" s="39"/>
       <c r="B22" s="17" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="37"/>
+      <c r="A23" s="39"/>
       <c r="B23" s="17" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="37"/>
+      <c r="A24" s="39"/>
       <c r="B24" s="17" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="37">
+      <c r="A25" s="39">
         <v>4</v>
       </c>
       <c r="B25" s="17" t="s">
@@ -14141,37 +14141,37 @@
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="37"/>
+      <c r="A26" s="39"/>
       <c r="B26" s="17" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="37"/>
+      <c r="A27" s="39"/>
       <c r="B27" s="17" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="37"/>
+      <c r="A28" s="39"/>
       <c r="B28" s="17" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="37"/>
+      <c r="A29" s="39"/>
       <c r="B29" s="17" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="37"/>
+      <c r="A30" s="39"/>
       <c r="B30" s="17" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="37">
+      <c r="A31" s="39">
         <v>5</v>
       </c>
       <c r="B31" s="17" t="s">
@@ -14179,31 +14179,31 @@
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="37"/>
+      <c r="A32" s="39"/>
       <c r="B32" s="17" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="37"/>
+      <c r="A33" s="39"/>
       <c r="B33" s="17" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="37"/>
+      <c r="A34" s="39"/>
       <c r="B34" s="17" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="37"/>
+      <c r="A35" s="39"/>
       <c r="B35" s="17" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="37">
+      <c r="A36" s="39">
         <v>6</v>
       </c>
       <c r="B36" s="17" t="s">
@@ -14211,31 +14211,31 @@
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="37"/>
+      <c r="A37" s="39"/>
       <c r="B37" s="17" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="37"/>
+      <c r="A38" s="39"/>
       <c r="B38" s="17" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="37"/>
+      <c r="A39" s="39"/>
       <c r="B39" s="17" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="37"/>
+      <c r="A40" s="39"/>
       <c r="B40" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="37">
+      <c r="A41" s="39">
         <v>7</v>
       </c>
       <c r="B41" s="17" t="s">
@@ -14243,25 +14243,25 @@
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="37"/>
+      <c r="A42" s="39"/>
       <c r="B42" s="17" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="37"/>
+      <c r="A43" s="39"/>
       <c r="B43" s="17" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="37"/>
+      <c r="A44" s="39"/>
       <c r="B44" s="17" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="37">
+      <c r="A45" s="39">
         <v>8</v>
       </c>
       <c r="B45" s="17" t="s">
@@ -14269,25 +14269,25 @@
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="37"/>
+      <c r="A46" s="39"/>
       <c r="B46" s="17" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="37"/>
+      <c r="A47" s="39"/>
       <c r="B47" s="17" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="37"/>
+      <c r="A48" s="39"/>
       <c r="B48" s="17" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="37">
+      <c r="A49" s="39">
         <v>9</v>
       </c>
       <c r="B49" s="17" t="s">
@@ -14295,31 +14295,31 @@
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="37"/>
+      <c r="A50" s="39"/>
       <c r="B50" s="17" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="37"/>
+      <c r="A51" s="39"/>
       <c r="B51" s="17" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="37"/>
+      <c r="A52" s="39"/>
       <c r="B52" s="17" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="37"/>
+      <c r="A53" s="39"/>
       <c r="B53" s="17" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="37">
+      <c r="A54" s="39">
         <v>10</v>
       </c>
       <c r="B54" s="17" t="s">
@@ -14327,25 +14327,25 @@
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="37"/>
+      <c r="A55" s="39"/>
       <c r="B55" s="17" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="37"/>
+      <c r="A56" s="39"/>
       <c r="B56" s="17" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="37"/>
+      <c r="A57" s="39"/>
       <c r="B57" s="17" t="s">
         <v>666</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="37">
+      <c r="A58" s="39">
         <v>11</v>
       </c>
       <c r="B58" s="17" t="s">
@@ -14353,49 +14353,49 @@
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="37"/>
+      <c r="A59" s="39"/>
       <c r="B59" s="17" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="37"/>
+      <c r="A60" s="39"/>
       <c r="B60" s="17" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="37"/>
+      <c r="A61" s="39"/>
       <c r="B61" s="17" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="37"/>
+      <c r="A62" s="39"/>
       <c r="B62" s="17" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="37"/>
+      <c r="A63" s="39"/>
       <c r="B63" s="17" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="37"/>
+      <c r="A64" s="39"/>
       <c r="B64" s="17" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="37"/>
+      <c r="A65" s="39"/>
       <c r="B65" s="17" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="37"/>
+      <c r="A66" s="39"/>
       <c r="B66" s="17" t="s">
         <v>667</v>
       </c>
@@ -14409,7 +14409,7 @@
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="37">
+      <c r="A68" s="39">
         <v>13</v>
       </c>
       <c r="B68" s="17" t="s">
@@ -14417,49 +14417,49 @@
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="37"/>
+      <c r="A69" s="39"/>
       <c r="B69" s="17" t="s">
         <v>670</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="37"/>
+      <c r="A70" s="39"/>
       <c r="B70" s="17" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="37"/>
+      <c r="A71" s="39"/>
       <c r="B71" s="17" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="37"/>
+      <c r="A72" s="39"/>
       <c r="B72" s="17" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="37"/>
+      <c r="A73" s="39"/>
       <c r="B73" s="17" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="37"/>
+      <c r="A74" s="39"/>
       <c r="B74" s="17" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="37"/>
+      <c r="A75" s="39"/>
       <c r="B75" s="17" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="37"/>
+      <c r="A76" s="39"/>
       <c r="B76" s="17" t="s">
         <v>379</v>
       </c>
@@ -14543,10 +14543,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="40" t="s">
         <v>671</v>
       </c>
-      <c r="B1" s="38"/>
+      <c r="B1" s="40"/>
     </row>
     <row r="2" spans="1:2" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -14557,7 +14557,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="37">
+      <c r="A3" s="39">
         <v>1</v>
       </c>
       <c r="B3" s="17" t="s">
@@ -14565,37 +14565,37 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="37"/>
+      <c r="A4" s="39"/>
       <c r="B4" s="17" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="37"/>
+      <c r="A5" s="39"/>
       <c r="B5" s="17" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="37"/>
+      <c r="A6" s="39"/>
       <c r="B6" s="17" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="37"/>
+      <c r="A7" s="39"/>
       <c r="B7" s="17" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="37"/>
+      <c r="A8" s="39"/>
       <c r="B8" s="17" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="37">
+      <c r="A9" s="39">
         <v>2</v>
       </c>
       <c r="B9" s="17" t="s">
@@ -14603,31 +14603,31 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="37"/>
+      <c r="A10" s="39"/>
       <c r="B10" s="17" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="37"/>
+      <c r="A11" s="39"/>
       <c r="B11" s="17" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="37"/>
+      <c r="A12" s="39"/>
       <c r="B12" s="17" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="37"/>
+      <c r="A13" s="39"/>
       <c r="B13" s="17" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="37">
+      <c r="A14" s="39">
         <v>3</v>
       </c>
       <c r="B14" s="17" t="s">
@@ -14635,31 +14635,31 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="37"/>
+      <c r="A15" s="39"/>
       <c r="B15" s="17" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="37"/>
+      <c r="A16" s="39"/>
       <c r="B16" s="17" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
+      <c r="A17" s="39"/>
       <c r="B17" s="17" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="37"/>
+      <c r="A18" s="39"/>
       <c r="B18" s="17" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="37">
+      <c r="A19" s="39">
         <v>4</v>
       </c>
       <c r="B19" s="17" t="s">
@@ -14667,73 +14667,73 @@
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="37"/>
+      <c r="A20" s="39"/>
       <c r="B20" s="17" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="37"/>
+      <c r="A21" s="39"/>
       <c r="B21" s="17" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="37"/>
+      <c r="A22" s="39"/>
       <c r="B22" s="17" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="37"/>
+      <c r="A23" s="39"/>
       <c r="B23" s="17" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="37"/>
+      <c r="A24" s="39"/>
       <c r="B24" s="17" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="37"/>
+      <c r="A25" s="39"/>
       <c r="B25" s="17" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="37"/>
+      <c r="A26" s="39"/>
       <c r="B26" s="17" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="37"/>
+      <c r="A27" s="39"/>
       <c r="B27" s="17" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="37"/>
+      <c r="A28" s="39"/>
       <c r="B28" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="37"/>
+      <c r="A29" s="39"/>
       <c r="B29" s="17" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="37"/>
+      <c r="A30" s="39"/>
       <c r="B30" s="17" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="37">
+      <c r="A31" s="39">
         <v>5</v>
       </c>
       <c r="B31" s="17" t="s">
@@ -14741,25 +14741,25 @@
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="37"/>
+      <c r="A32" s="39"/>
       <c r="B32" s="17" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="37"/>
+      <c r="A33" s="39"/>
       <c r="B33" s="17" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="37"/>
+      <c r="A34" s="39"/>
       <c r="B34" s="17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="37">
+      <c r="A35" s="39">
         <v>6</v>
       </c>
       <c r="B35" s="17" t="s">
@@ -14767,31 +14767,31 @@
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="37"/>
+      <c r="A36" s="39"/>
       <c r="B36" s="17" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="37"/>
+      <c r="A37" s="39"/>
       <c r="B37" s="17" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="37"/>
+      <c r="A38" s="39"/>
       <c r="B38" s="17" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="37"/>
+      <c r="A39" s="39"/>
       <c r="B39" s="17" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="37">
+      <c r="A40" s="39">
         <v>7</v>
       </c>
       <c r="B40" s="17" t="s">
@@ -14799,25 +14799,25 @@
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="37"/>
+      <c r="A41" s="39"/>
       <c r="B41" s="17" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="37"/>
+      <c r="A42" s="39"/>
       <c r="B42" s="17" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="37"/>
+      <c r="A43" s="39"/>
       <c r="B43" s="17" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="37">
+      <c r="A44" s="39">
         <v>8</v>
       </c>
       <c r="B44" s="17" t="s">
@@ -14825,31 +14825,31 @@
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="37"/>
+      <c r="A45" s="39"/>
       <c r="B45" s="17" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="37"/>
+      <c r="A46" s="39"/>
       <c r="B46" s="17" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="37"/>
+      <c r="A47" s="39"/>
       <c r="B47" s="17" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="37"/>
+      <c r="A48" s="39"/>
       <c r="B48" s="17" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="37">
+      <c r="A49" s="39">
         <v>9</v>
       </c>
       <c r="B49" s="17" t="s">
@@ -14857,31 +14857,31 @@
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="37"/>
+      <c r="A50" s="39"/>
       <c r="B50" s="17" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="37"/>
+      <c r="A51" s="39"/>
       <c r="B51" s="17" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="37"/>
+      <c r="A52" s="39"/>
       <c r="B52" s="17" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="37"/>
+      <c r="A53" s="39"/>
       <c r="B53" s="17" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="37">
+      <c r="A54" s="39">
         <v>10</v>
       </c>
       <c r="B54" s="17" t="s">
@@ -14889,31 +14889,31 @@
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="37"/>
+      <c r="A55" s="39"/>
       <c r="B55" s="17" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="37"/>
+      <c r="A56" s="39"/>
       <c r="B56" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="37"/>
+      <c r="A57" s="39"/>
       <c r="B57" s="17" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="37"/>
+      <c r="A58" s="39"/>
       <c r="B58" s="17" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="37">
+      <c r="A59" s="39">
         <v>11</v>
       </c>
       <c r="B59" s="17" t="s">
@@ -14921,43 +14921,43 @@
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="37"/>
+      <c r="A60" s="39"/>
       <c r="B60" s="17" t="s">
         <v>588</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="37"/>
+      <c r="A61" s="39"/>
       <c r="B61" s="17" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="37"/>
+      <c r="A62" s="39"/>
       <c r="B62" s="17" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="37"/>
+      <c r="A63" s="39"/>
       <c r="B63" s="17" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="37"/>
+      <c r="A64" s="39"/>
       <c r="B64" s="17" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="37"/>
+      <c r="A65" s="39"/>
       <c r="B65" s="17" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="37">
+      <c r="A66" s="39">
         <v>12</v>
       </c>
       <c r="B66" s="17" t="s">
@@ -14965,55 +14965,55 @@
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="37"/>
+      <c r="A67" s="39"/>
       <c r="B67" s="17" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="37"/>
+      <c r="A68" s="39"/>
       <c r="B68" s="17" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="37"/>
+      <c r="A69" s="39"/>
       <c r="B69" s="17" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="37"/>
+      <c r="A70" s="39"/>
       <c r="B70" s="17" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="37"/>
+      <c r="A71" s="39"/>
       <c r="B71" s="17" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="37"/>
+      <c r="A72" s="39"/>
       <c r="B72" s="17" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="37"/>
+      <c r="A73" s="39"/>
       <c r="B73" s="17" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="37"/>
+      <c r="A74" s="39"/>
       <c r="B74" s="17" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="37"/>
+      <c r="A75" s="39"/>
       <c r="B75" s="17" t="s">
         <v>421</v>
       </c>
@@ -15129,10 +15129,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="40" t="s">
         <v>672</v>
       </c>
-      <c r="B1" s="38"/>
+      <c r="B1" s="40"/>
     </row>
     <row r="2" spans="1:2" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -15143,7 +15143,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="37">
+      <c r="A3" s="39">
         <v>1</v>
       </c>
       <c r="B3" s="17" t="s">
@@ -15151,37 +15151,37 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="37"/>
+      <c r="A4" s="39"/>
       <c r="B4" s="17" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="37"/>
+      <c r="A5" s="39"/>
       <c r="B5" s="17" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="37"/>
+      <c r="A6" s="39"/>
       <c r="B6" s="17" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="37"/>
+      <c r="A7" s="39"/>
       <c r="B7" s="17" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="37"/>
+      <c r="A8" s="39"/>
       <c r="B8" s="17" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="37">
+      <c r="A9" s="39">
         <v>2</v>
       </c>
       <c r="B9" s="17" t="s">
@@ -15189,31 +15189,31 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="37"/>
+      <c r="A10" s="39"/>
       <c r="B10" s="17" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="37"/>
+      <c r="A11" s="39"/>
       <c r="B11" s="17" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="37"/>
+      <c r="A12" s="39"/>
       <c r="B12" s="17" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="37"/>
+      <c r="A13" s="39"/>
       <c r="B13" s="17" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="37">
+      <c r="A14" s="39">
         <v>3</v>
       </c>
       <c r="B14" s="17" t="s">
@@ -15221,79 +15221,79 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="37"/>
+      <c r="A15" s="39"/>
       <c r="B15" s="17" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="37"/>
+      <c r="A16" s="39"/>
       <c r="B16" s="17" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
+      <c r="A17" s="39"/>
       <c r="B17" s="17" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="37"/>
+      <c r="A18" s="39"/>
       <c r="B18" s="17" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="37"/>
+      <c r="A19" s="39"/>
       <c r="B19" s="17" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="37"/>
+      <c r="A20" s="39"/>
       <c r="B20" s="17" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="37"/>
+      <c r="A21" s="39"/>
       <c r="B21" s="17" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="37"/>
+      <c r="A22" s="39"/>
       <c r="B22" s="17" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="37"/>
+      <c r="A23" s="39"/>
       <c r="B23" s="17" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="37"/>
+      <c r="A24" s="39"/>
       <c r="B24" s="17" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="37"/>
+      <c r="A25" s="39"/>
       <c r="B25" s="17" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="37"/>
+      <c r="A26" s="39"/>
       <c r="B26" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="37">
+      <c r="A27" s="39">
         <v>4</v>
       </c>
       <c r="B27" s="17" t="s">
@@ -15301,43 +15301,43 @@
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="37"/>
+      <c r="A28" s="39"/>
       <c r="B28" s="17" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="37"/>
+      <c r="A29" s="39"/>
       <c r="B29" s="17" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="37"/>
+      <c r="A30" s="39"/>
       <c r="B30" s="17" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="37"/>
+      <c r="A31" s="39"/>
       <c r="B31" s="17" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="37"/>
+      <c r="A32" s="39"/>
       <c r="B32" s="17" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="37"/>
+      <c r="A33" s="39"/>
       <c r="B33" s="17" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="37">
+      <c r="A34" s="39">
         <v>5</v>
       </c>
       <c r="B34" s="17" t="s">
@@ -15345,31 +15345,31 @@
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="37"/>
+      <c r="A35" s="39"/>
       <c r="B35" s="17" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="37"/>
+      <c r="A36" s="39"/>
       <c r="B36" s="17" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="37"/>
+      <c r="A37" s="39"/>
       <c r="B37" s="17" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="37"/>
+      <c r="A38" s="39"/>
       <c r="B38" s="17" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="37">
+      <c r="A39" s="39">
         <v>6</v>
       </c>
       <c r="B39" s="17" t="s">
@@ -15377,25 +15377,25 @@
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="37"/>
+      <c r="A40" s="39"/>
       <c r="B40" s="17" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="37"/>
+      <c r="A41" s="39"/>
       <c r="B41" s="17" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="37"/>
+      <c r="A42" s="39"/>
       <c r="B42" s="17" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="37">
+      <c r="A43" s="39">
         <v>7</v>
       </c>
       <c r="B43" s="17" t="s">
@@ -15403,31 +15403,31 @@
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="37"/>
+      <c r="A44" s="39"/>
       <c r="B44" s="17" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="37"/>
+      <c r="A45" s="39"/>
       <c r="B45" s="17" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="37"/>
+      <c r="A46" s="39"/>
       <c r="B46" s="17" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="37"/>
+      <c r="A47" s="39"/>
       <c r="B47" s="17" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="37">
+      <c r="A48" s="39">
         <v>8</v>
       </c>
       <c r="B48" s="17" t="s">
@@ -15435,49 +15435,49 @@
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="37"/>
+      <c r="A49" s="39"/>
       <c r="B49" s="17" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="37"/>
+      <c r="A50" s="39"/>
       <c r="B50" s="17" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="37"/>
+      <c r="A51" s="39"/>
       <c r="B51" s="17" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="37"/>
+      <c r="A52" s="39"/>
       <c r="B52" s="17" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="37"/>
+      <c r="A53" s="39"/>
       <c r="B53" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="37"/>
+      <c r="A54" s="39"/>
       <c r="B54" s="17" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="37"/>
+      <c r="A55" s="39"/>
       <c r="B55" s="17" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="37">
+      <c r="A56" s="39">
         <v>9</v>
       </c>
       <c r="B56" s="17" t="s">
@@ -15485,55 +15485,55 @@
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="37"/>
+      <c r="A57" s="39"/>
       <c r="B57" s="17" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="37"/>
+      <c r="A58" s="39"/>
       <c r="B58" s="17" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="37"/>
+      <c r="A59" s="39"/>
       <c r="B59" s="17" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="37"/>
+      <c r="A60" s="39"/>
       <c r="B60" s="17" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="37"/>
+      <c r="A61" s="39"/>
       <c r="B61" s="17" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="37"/>
+      <c r="A62" s="39"/>
       <c r="B62" s="17" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="37"/>
+      <c r="A63" s="39"/>
       <c r="B63" s="17" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="37"/>
+      <c r="A64" s="39"/>
       <c r="B64" s="17" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="37">
+      <c r="A65" s="39">
         <v>10</v>
       </c>
       <c r="B65" s="17" t="s">
@@ -15541,49 +15541,49 @@
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="37"/>
+      <c r="A66" s="39"/>
       <c r="B66" s="17" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="37"/>
+      <c r="A67" s="39"/>
       <c r="B67" s="17" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="37"/>
+      <c r="A68" s="39"/>
       <c r="B68" s="17" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="37"/>
+      <c r="A69" s="39"/>
       <c r="B69" s="17" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="37"/>
+      <c r="A70" s="39"/>
       <c r="B70" s="17" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="37"/>
+      <c r="A71" s="39"/>
       <c r="B71" s="17" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="37"/>
+      <c r="A72" s="39"/>
       <c r="B72" s="17" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="37"/>
+      <c r="A73" s="39"/>
       <c r="B73" s="17" t="s">
         <v>309</v>
       </c>
@@ -15597,7 +15597,7 @@
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="37">
+      <c r="A75" s="39">
         <v>12</v>
       </c>
       <c r="B75" s="17" t="s">
@@ -15605,67 +15605,67 @@
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="37"/>
+      <c r="A76" s="39"/>
       <c r="B76" s="17" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="37"/>
+      <c r="A77" s="39"/>
       <c r="B77" s="17" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="37"/>
+      <c r="A78" s="39"/>
       <c r="B78" s="17" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="37"/>
+      <c r="A79" s="39"/>
       <c r="B79" s="17" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="37"/>
+      <c r="A80" s="39"/>
       <c r="B80" s="17" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" s="37"/>
+      <c r="A81" s="39"/>
       <c r="B81" s="17" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" s="37"/>
+      <c r="A82" s="39"/>
       <c r="B82" s="17" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" s="37"/>
+      <c r="A83" s="39"/>
       <c r="B83" s="17" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84" s="37"/>
+      <c r="A84" s="39"/>
       <c r="B84" s="17" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85" s="37"/>
+      <c r="A85" s="39"/>
       <c r="B85" s="17" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86" s="37"/>
+      <c r="A86" s="39"/>
       <c r="B86" s="17" t="s">
         <v>127</v>
       </c>
@@ -15707,10 +15707,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="40" t="s">
         <v>673</v>
       </c>
-      <c r="B1" s="38"/>
+      <c r="B1" s="40"/>
     </row>
     <row r="2" spans="1:2" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -15721,7 +15721,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="37">
+      <c r="A3" s="39">
         <v>1</v>
       </c>
       <c r="B3" s="19" t="s">
@@ -15729,37 +15729,37 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="37"/>
+      <c r="A4" s="39"/>
       <c r="B4" s="19" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="37"/>
+      <c r="A5" s="39"/>
       <c r="B5" s="19" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="37"/>
+      <c r="A6" s="39"/>
       <c r="B6" s="19" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="37"/>
+      <c r="A7" s="39"/>
       <c r="B7" s="19" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="37"/>
+      <c r="A8" s="39"/>
       <c r="B8" s="19" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="37">
+      <c r="A9" s="39">
         <v>2</v>
       </c>
       <c r="B9" s="23" t="s">
@@ -15767,31 +15767,31 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="37"/>
+      <c r="A10" s="39"/>
       <c r="B10" s="23" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="37"/>
+      <c r="A11" s="39"/>
       <c r="B11" s="17" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="37"/>
+      <c r="A12" s="39"/>
       <c r="B12" s="17" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="37"/>
+      <c r="A13" s="39"/>
       <c r="B13" s="17" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="37">
+      <c r="A14" s="39">
         <v>3</v>
       </c>
       <c r="B14" s="17" t="s">
@@ -15799,37 +15799,37 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="37"/>
+      <c r="A15" s="39"/>
       <c r="B15" s="17" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="37"/>
+      <c r="A16" s="39"/>
       <c r="B16" s="17" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
+      <c r="A17" s="39"/>
       <c r="B17" s="17" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="37"/>
+      <c r="A18" s="39"/>
       <c r="B18" s="17" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="37"/>
+      <c r="A19" s="39"/>
       <c r="B19" s="17" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="37">
+      <c r="A20" s="39">
         <v>4</v>
       </c>
       <c r="B20" s="17" t="s">
@@ -15837,37 +15837,37 @@
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="37"/>
+      <c r="A21" s="39"/>
       <c r="B21" s="17" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="37"/>
+      <c r="A22" s="39"/>
       <c r="B22" s="17" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="37"/>
+      <c r="A23" s="39"/>
       <c r="B23" s="17" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="37"/>
+      <c r="A24" s="39"/>
       <c r="B24" s="17" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="37"/>
+      <c r="A25" s="39"/>
       <c r="B25" s="17" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="37">
+      <c r="A26" s="39">
         <v>5</v>
       </c>
       <c r="B26" s="17" t="s">
@@ -15875,25 +15875,25 @@
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="37"/>
+      <c r="A27" s="39"/>
       <c r="B27" s="17" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="37"/>
+      <c r="A28" s="39"/>
       <c r="B28" s="17" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="37"/>
+      <c r="A29" s="39"/>
       <c r="B29" s="17" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="37">
+      <c r="A30" s="39">
         <v>6</v>
       </c>
       <c r="B30" s="17" t="s">
@@ -15901,31 +15901,31 @@
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="37"/>
+      <c r="A31" s="39"/>
       <c r="B31" s="17" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="37"/>
+      <c r="A32" s="39"/>
       <c r="B32" s="17" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="37"/>
+      <c r="A33" s="39"/>
       <c r="B33" s="17" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="37"/>
+      <c r="A34" s="39"/>
       <c r="B34" s="17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="37">
+      <c r="A35" s="39">
         <v>7</v>
       </c>
       <c r="B35" s="17" t="s">
@@ -15933,31 +15933,31 @@
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="37"/>
+      <c r="A36" s="39"/>
       <c r="B36" s="17" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="37"/>
+      <c r="A37" s="39"/>
       <c r="B37" s="17" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="37"/>
+      <c r="A38" s="39"/>
       <c r="B38" s="17" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="37"/>
+      <c r="A39" s="39"/>
       <c r="B39" s="17" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="37">
+      <c r="A40" s="39">
         <v>8</v>
       </c>
       <c r="B40" s="17" t="s">
@@ -15965,67 +15965,67 @@
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="37"/>
+      <c r="A41" s="39"/>
       <c r="B41" s="17" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="37"/>
+      <c r="A42" s="39"/>
       <c r="B42" s="17" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="37"/>
+      <c r="A43" s="39"/>
       <c r="B43" s="17" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="37"/>
+      <c r="A44" s="39"/>
       <c r="B44" s="19" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="37"/>
+      <c r="A45" s="39"/>
       <c r="B45" s="19" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="37"/>
+      <c r="A46" s="39"/>
       <c r="B46" s="19" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="37"/>
+      <c r="A47" s="39"/>
       <c r="B47" s="19" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="37"/>
+      <c r="A48" s="39"/>
       <c r="B48" s="19" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="37"/>
+      <c r="A49" s="39"/>
       <c r="B49" s="19" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="37"/>
+      <c r="A50" s="39"/>
       <c r="B50" s="19" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="37">
+      <c r="A51" s="39">
         <v>9</v>
       </c>
       <c r="B51" s="17" t="s">
@@ -16033,55 +16033,55 @@
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="37"/>
+      <c r="A52" s="39"/>
       <c r="B52" s="17" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="37"/>
+      <c r="A53" s="39"/>
       <c r="B53" s="17" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="37"/>
+      <c r="A54" s="39"/>
       <c r="B54" s="17" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="37"/>
+      <c r="A55" s="39"/>
       <c r="B55" s="17" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="37"/>
+      <c r="A56" s="39"/>
       <c r="B56" s="17" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="37"/>
+      <c r="A57" s="39"/>
       <c r="B57" s="17" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="37"/>
+      <c r="A58" s="39"/>
       <c r="B58" s="17" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="37"/>
+      <c r="A59" s="39"/>
       <c r="B59" s="17" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="37">
+      <c r="A60" s="39">
         <v>10</v>
       </c>
       <c r="B60" s="17" t="s">
@@ -16089,73 +16089,73 @@
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="37"/>
+      <c r="A61" s="39"/>
       <c r="B61" s="17" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="37"/>
+      <c r="A62" s="39"/>
       <c r="B62" s="17" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="37"/>
+      <c r="A63" s="39"/>
       <c r="B63" s="17" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="37"/>
+      <c r="A64" s="39"/>
       <c r="B64" s="17" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="37"/>
+      <c r="A65" s="39"/>
       <c r="B65" s="17" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="37"/>
+      <c r="A66" s="39"/>
       <c r="B66" s="17" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="37"/>
+      <c r="A67" s="39"/>
       <c r="B67" s="17" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="37"/>
+      <c r="A68" s="39"/>
       <c r="B68" s="17" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="37"/>
+      <c r="A69" s="39"/>
       <c r="B69" s="17" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="37"/>
+      <c r="A70" s="39"/>
       <c r="B70" s="17" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="37"/>
+      <c r="A71" s="39"/>
       <c r="B71" s="17" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="37">
+      <c r="A72" s="39">
         <v>11</v>
       </c>
       <c r="B72" s="17" t="s">
@@ -16163,25 +16163,25 @@
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="37"/>
+      <c r="A73" s="39"/>
       <c r="B73" s="17" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="37"/>
+      <c r="A74" s="39"/>
       <c r="B74" s="17" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="37"/>
+      <c r="A75" s="39"/>
       <c r="B75" s="17" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="37">
+      <c r="A76" s="39">
         <v>12</v>
       </c>
       <c r="B76" s="17" t="s">
@@ -16189,73 +16189,73 @@
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="37"/>
+      <c r="A77" s="39"/>
       <c r="B77" s="17" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="37"/>
+      <c r="A78" s="39"/>
       <c r="B78" s="17" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="37"/>
+      <c r="A79" s="39"/>
       <c r="B79" s="17" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="37"/>
+      <c r="A80" s="39"/>
       <c r="B80" s="17" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" s="37"/>
+      <c r="A81" s="39"/>
       <c r="B81" s="17" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" s="37"/>
+      <c r="A82" s="39"/>
       <c r="B82" s="17" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" s="37"/>
+      <c r="A83" s="39"/>
       <c r="B83" s="17" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84" s="37"/>
+      <c r="A84" s="39"/>
       <c r="B84" s="17" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85" s="37"/>
+      <c r="A85" s="39"/>
       <c r="B85" s="17" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86" s="37"/>
+      <c r="A86" s="39"/>
       <c r="B86" s="17" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A87" s="37"/>
+      <c r="A87" s="39"/>
       <c r="B87" s="17" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A88" s="37"/>
+      <c r="A88" s="39"/>
       <c r="B88" s="17" t="s">
         <v>316</v>
       </c>
@@ -16270,12 +16270,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A76:A88"/>
     <mergeCell ref="A30:A34"/>
     <mergeCell ref="A35:A39"/>
@@ -16283,6 +16277,12 @@
     <mergeCell ref="A51:A59"/>
     <mergeCell ref="A60:A71"/>
     <mergeCell ref="A72:A75"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
